--- a/parametres_simulateur_inphb.xlsx
+++ b/parametres_simulateur_inphb.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0bc125c4368f47fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coefficients_bac" sheetId="2" r:id="Rf8abc7dcda8b4179"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coefficients_inphb" sheetId="3" r:id="R32474a34932142c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eligibilite_inphb" sheetId="4" r:id="R39ed76f6340b45b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="places_estimees" sheetId="5" r:id="R275ffc48bf6544ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mentions_inphb" sheetId="6" r:id="Rce537ed17caf48b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stats_series_2025" sheetId="7" r:id="Re21e8c81ada0440d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="groupes_matieres" sheetId="8" r:id="R3d95fceb73e4425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R00e36fb9fed24cae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coefficients_bac" sheetId="2" r:id="Ra878fc66adcb4ee9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coefficients_inphb" sheetId="3" r:id="Radd5faa3790b47f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eligibilite_inphb" sheetId="4" r:id="R28ded44607bd4160"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="places_estimees" sheetId="5" r:id="R291c1041482d4331"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mentions_inphb" sheetId="6" r:id="Rab0bf131908a4e55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stats_series_2025" sheetId="7" r:id="Re403d86b53fb4a42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="groupes_matieres" sheetId="8" r:id="R9577b12d26e44cbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="liens_filieres" sheetId="9" r:id="Rf9716bd00cb14b0c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -702,7 +703,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -739,9 +740,42 @@
         <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF123B5D"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="9">
     <x:border diagonalUp="0" diagonalDown="0"/>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left/>
+      <x:top/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:top/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right/>
+      <x:top/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left/>
+      <x:bottom/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:bottom/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right/>
+      <x:bottom/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="26">
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -775,7 +809,7 @@
     </x:xf>
     <x:xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="1" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="47">
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="0" applyBorder="0" applyAlignment="0">
       <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -862,6 +896,60 @@
     </x:xf>
     <x:xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="12">
@@ -4276,7 +4364,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R164ed97395804641"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc40af47fe8b4be6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8122,7 +8210,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0ea01c806254178"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ae0b812ea0447b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9229,7 +9317,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40fd5fc8068a4c89"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R815e67d27ee24e50"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10254,7 +10342,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ef610a289134f65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree55753f34fe4d64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11104,7 +11192,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f2b5a732fc342a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R102caef4985c4757"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12296,7 +12384,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bb6216296fe48af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb6d4a5fe3c14c82"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14556,4 +14644,390 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="44" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="55" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="38" t="str">
+        <x:v>filiere</x:v>
+      </x:c>
+      <x:c r="B1" s="39" t="str">
+        <x:v>ecole</x:v>
+      </x:c>
+      <x:c r="C1" s="39" t="str">
+        <x:v>cycle</x:v>
+      </x:c>
+      <x:c r="D1" s="39" t="str">
+        <x:v>intitule</x:v>
+      </x:c>
+      <x:c r="E1" s="39" t="str">
+        <x:v>url_officielle</x:v>
+      </x:c>
+      <x:c r="F1" s="39" t="str">
+        <x:v>type_lien</x:v>
+      </x:c>
+      <x:c r="G1" s="40" t="str">
+        <x:v>commentaire</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="34" customHeight="1">
+      <x:c r="A2" s="41" t="str">
+        <x:v>GAE</x:v>
+      </x:c>
+      <x:c r="B2" s="42" t="str">
+        <x:v>ESCAE</x:v>
+      </x:c>
+      <x:c r="C2" s="42" t="str">
+        <x:v>Cycle court</x:v>
+      </x:c>
+      <x:c r="D2" s="42" t="str">
+        <x:v>Gestion appliquée aux entreprises</x:v>
+      </x:c>
+      <x:c r="E2" s="42" t="str">
+        <x:v>https://escae.inphb.ci/public/formations</x:v>
+      </x:c>
+      <x:c r="F2" s="42" t="str">
+        <x:v>Page de l'école</x:v>
+      </x:c>
+      <x:c r="G2" s="43" t="str">
+        <x:v>Offre de formation officielle de l'ESCAE.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="34" customHeight="1">
+      <x:c r="A3" s="41" t="str">
+        <x:v>FCA</x:v>
+      </x:c>
+      <x:c r="B3" s="42" t="str">
+        <x:v>ESCAE</x:v>
+      </x:c>
+      <x:c r="C3" s="42" t="str">
+        <x:v>Cycle court</x:v>
+      </x:c>
+      <x:c r="D3" s="42" t="str">
+        <x:v>Finance, comptabilité et audit</x:v>
+      </x:c>
+      <x:c r="E3" s="42" t="str">
+        <x:v>https://escae.inphb.ci/public/formations</x:v>
+      </x:c>
+      <x:c r="F3" s="42" t="str">
+        <x:v>Page de l'école</x:v>
+      </x:c>
+      <x:c r="G3" s="43" t="str">
+        <x:v>Offre de formation officielle de l'ESCAE.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="34" customHeight="1">
+      <x:c r="A4" s="41" t="str">
+        <x:v>ECG</x:v>
+      </x:c>
+      <x:c r="B4" s="42" t="str">
+        <x:v>CPGE</x:v>
+      </x:c>
+      <x:c r="C4" s="42" t="str">
+        <x:v>Cycle préparatoire</x:v>
+      </x:c>
+      <x:c r="D4" s="42" t="str">
+        <x:v>Économique et commerciale générale</x:v>
+      </x:c>
+      <x:c r="E4" s="42" t="str">
+        <x:v>https://www.inphb.ci/static/media/CPGE.9b4d786a11dd59ac7ac1.pdf</x:v>
+      </x:c>
+      <x:c r="F4" s="42" t="str">
+        <x:v>Plaquette officielle</x:v>
+      </x:c>
+      <x:c r="G4" s="43" t="str">
+        <x:v>Plaquette officielle des classes préparatoires de l'INP-HB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="34" customHeight="1">
+      <x:c r="A5" s="41" t="str">
+        <x:v>BCPST</x:v>
+      </x:c>
+      <x:c r="B5" s="42" t="str">
+        <x:v>CPGE</x:v>
+      </x:c>
+      <x:c r="C5" s="42" t="str">
+        <x:v>Cycle préparatoire</x:v>
+      </x:c>
+      <x:c r="D5" s="42" t="str">
+        <x:v>Biologie, chimie, physique et sciences de la Terre</x:v>
+      </x:c>
+      <x:c r="E5" s="42" t="str">
+        <x:v>https://www.inphb.ci/static/media/CPGE.9b4d786a11dd59ac7ac1.pdf</x:v>
+      </x:c>
+      <x:c r="F5" s="42" t="str">
+        <x:v>Plaquette officielle</x:v>
+      </x:c>
+      <x:c r="G5" s="43" t="str">
+        <x:v>Plaquette officielle des classes préparatoires de l'INP-HB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="34" customHeight="1">
+      <x:c r="A6" s="41" t="str">
+        <x:v>MPSI</x:v>
+      </x:c>
+      <x:c r="B6" s="42" t="str">
+        <x:v>CPGE</x:v>
+      </x:c>
+      <x:c r="C6" s="42" t="str">
+        <x:v>Cycle préparatoire</x:v>
+      </x:c>
+      <x:c r="D6" s="42" t="str">
+        <x:v>Mathématiques, physique et sciences de l'ingénieur</x:v>
+      </x:c>
+      <x:c r="E6" s="42" t="str">
+        <x:v>https://www.inphb.ci/static/media/CPGE.9b4d786a11dd59ac7ac1.pdf</x:v>
+      </x:c>
+      <x:c r="F6" s="42" t="str">
+        <x:v>Plaquette officielle</x:v>
+      </x:c>
+      <x:c r="G6" s="43" t="str">
+        <x:v>Plaquette officielle des classes préparatoires de l'INP-HB.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="34" customHeight="1">
+      <x:c r="A7" s="41" t="str">
+        <x:v>MP2I</x:v>
+      </x:c>
+      <x:c r="B7" s="42" t="str">
+        <x:v>CPGE</x:v>
+      </x:c>
+      <x:c r="C7" s="42" t="str">
+        <x:v>Cycle préparatoire</x:v>
+      </x:c>
+      <x:c r="D7" s="42" t="str">
+        <x:v>Mathématiques, physique, ingénierie et informatique</x:v>
+      </x:c>
+      <x:c r="E7" s="42" t="str">
+        <x:v>https://www.inphb.ci/static/media/CPGE.9b4d786a11dd59ac7ac1.pdf</x:v>
+      </x:c>
+      <x:c r="F7" s="42" t="str">
+        <x:v>Plaquette officielle</x:v>
+      </x:c>
+      <x:c r="G7" s="43" t="str">
+        <x:v>Lien vers la présentation officielle des classes préparatoires ; la plaquette publiée peut ne pas détailler cette voie récente.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="34" customHeight="1">
+      <x:c r="A8" s="41" t="str">
+        <x:v>PCSI</x:v>
+      </x:c>
+      <x:c r="B8" s="42" t="str">
+        <x:v>CPGE</x:v>
+      </x:c>
+      <x:c r="C8" s="42" t="str">
+        <x:v>Cycle préparatoire</x:v>
+      </x:c>
+      <x:c r="D8" s="42" t="str">
+        <x:v>Physique, chimie et sciences de l'ingénieur</x:v>
+      </x:c>
+      <x:c r="E8" s="42" t="str">
+        <x:v>https://www.inphb.ci/static/media/CPGE.9b4d786a11dd59ac7ac1.pdf</x:v>
+      </x:c>
+      <x:c r="F8" s="42" t="str">
+        <x:v>Plaquette officielle</x:v>
+      </x:c>
+      <x:c r="G8" s="43" t="str">
+        <x:v>Lien vers la présentation officielle des classes préparatoires ; la plaquette publiée peut ne pas détailler cette voie récente.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="34" customHeight="1">
+      <x:c r="A9" s="41" t="str">
+        <x:v>TSA</x:v>
+      </x:c>
+      <x:c r="B9" s="42" t="str">
+        <x:v>ESA</x:v>
+      </x:c>
+      <x:c r="C9" s="42" t="str">
+        <x:v>Cycle court</x:v>
+      </x:c>
+      <x:c r="D9" s="42" t="str">
+        <x:v>Technicien supérieur en agronomie</x:v>
+      </x:c>
+      <x:c r="E9" s="42" t="str">
+        <x:v>https://inphb.ci/static/media/ESA.1e3e6705a0c038fbfec7.pdf</x:v>
+      </x:c>
+      <x:c r="F9" s="42" t="str">
+        <x:v>Plaquette officielle</x:v>
+      </x:c>
+      <x:c r="G9" s="43" t="str">
+        <x:v>Plaquette officielle de l'École supérieure d'agronomie.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="34" customHeight="1">
+      <x:c r="A10" s="41" t="str">
+        <x:v>STIC</x:v>
+      </x:c>
+      <x:c r="B10" s="42" t="str">
+        <x:v>ESI</x:v>
+      </x:c>
+      <x:c r="C10" s="42" t="str">
+        <x:v>Cycle court</x:v>
+      </x:c>
+      <x:c r="D10" s="42" t="str">
+        <x:v>Sciences et technologies de l'information et de la communication</x:v>
+      </x:c>
+      <x:c r="E10" s="42" t="str">
+        <x:v>https://inphb.ci/static/media/ESI.6d5a13044a0918a30dd7.pdf</x:v>
+      </x:c>
+      <x:c r="F10" s="42" t="str">
+        <x:v>Plaquette officielle</x:v>
+      </x:c>
+      <x:c r="G10" s="43" t="str">
+        <x:v>Plaquette officielle de l'École supérieure d'industrie.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="34" customHeight="1">
+      <x:c r="A11" s="41" t="str">
+        <x:v>STGI</x:v>
+      </x:c>
+      <x:c r="B11" s="42" t="str">
+        <x:v>ESI</x:v>
+      </x:c>
+      <x:c r="C11" s="42" t="str">
+        <x:v>Cycle court</x:v>
+      </x:c>
+      <x:c r="D11" s="42" t="str">
+        <x:v>Sciences et technologies du génie industriel</x:v>
+      </x:c>
+      <x:c r="E11" s="42" t="str">
+        <x:v>https://inphb.ci/static/media/ESI.6d5a13044a0918a30dd7.pdf</x:v>
+      </x:c>
+      <x:c r="F11" s="42" t="str">
+        <x:v>Plaquette officielle</x:v>
+      </x:c>
+      <x:c r="G11" s="43" t="str">
+        <x:v>Plaquette officielle de l'École supérieure d'industrie.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="34" customHeight="1">
+      <x:c r="A12" s="41" t="str">
+        <x:v>GC</x:v>
+      </x:c>
+      <x:c r="B12" s="42" t="str">
+        <x:v>ESTP</x:v>
+      </x:c>
+      <x:c r="C12" s="42" t="str">
+        <x:v>Cycle court</x:v>
+      </x:c>
+      <x:c r="D12" s="42" t="str">
+        <x:v>Génie civil</x:v>
+      </x:c>
+      <x:c r="E12" s="42" t="str">
+        <x:v>https://inphb.ci/static/media/ESTP.fc83b695d74550741d9b.pdf</x:v>
+      </x:c>
+      <x:c r="F12" s="42" t="str">
+        <x:v>Plaquette officielle</x:v>
+      </x:c>
+      <x:c r="G12" s="43" t="str">
+        <x:v>Plaquette officielle de l'École supérieure des travaux publics.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="34" customHeight="1">
+      <x:c r="A13" s="41" t="str">
+        <x:v>MG</x:v>
+      </x:c>
+      <x:c r="B13" s="42" t="str">
+        <x:v>ESMG</x:v>
+      </x:c>
+      <x:c r="C13" s="42" t="str">
+        <x:v>Cycle court</x:v>
+      </x:c>
+      <x:c r="D13" s="42" t="str">
+        <x:v>Mines et géologie</x:v>
+      </x:c>
+      <x:c r="E13" s="42" t="str">
+        <x:v>https://inphb.ci/static/media/ESMG.3673dcbd14528ad175ac.pdf</x:v>
+      </x:c>
+      <x:c r="F13" s="42" t="str">
+        <x:v>Plaquette officielle</x:v>
+      </x:c>
+      <x:c r="G13" s="43" t="str">
+        <x:v>Plaquette officielle de l'École supérieure des mines et de géologie.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="34" customHeight="1">
+      <x:c r="A14" s="41" t="str">
+        <x:v>PME</x:v>
+      </x:c>
+      <x:c r="B14" s="42" t="str">
+        <x:v>ESCPE</x:v>
+      </x:c>
+      <x:c r="C14" s="42" t="str">
+        <x:v>Cycle court</x:v>
+      </x:c>
+      <x:c r="D14" s="42" t="str">
+        <x:v>Procédés et maîtrise de l'énergie</x:v>
+      </x:c>
+      <x:c r="E14" s="42" t="str">
+        <x:v>https://www.inphb.ci/</x:v>
+      </x:c>
+      <x:c r="F14" s="42" t="str">
+        <x:v>Site officiel INP-HB</x:v>
+      </x:c>
+      <x:c r="G14" s="43" t="str">
+        <x:v>Aucune fiche publique stable et spécifique n'a été identifiée ; lien vers le site officiel.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="34" customHeight="1">
+      <x:c r="A15" s="41" t="str">
+        <x:v>CGP</x:v>
+      </x:c>
+      <x:c r="B15" s="42" t="str">
+        <x:v>ESCPE</x:v>
+      </x:c>
+      <x:c r="C15" s="42" t="str">
+        <x:v>Cycle court</x:v>
+      </x:c>
+      <x:c r="D15" s="42" t="str">
+        <x:v>Chimie et génie des procédés</x:v>
+      </x:c>
+      <x:c r="E15" s="42" t="str">
+        <x:v>https://www.inphb.ci/</x:v>
+      </x:c>
+      <x:c r="F15" s="42" t="str">
+        <x:v>Site officiel INP-HB</x:v>
+      </x:c>
+      <x:c r="G15" s="43" t="str">
+        <x:v>Aucune fiche publique stable et spécifique n'a été identifiée ; lien vers le site officiel.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="34" customHeight="1">
+      <x:c r="A16" s="44" t="str">
+        <x:v>TSAERO</x:v>
+      </x:c>
+      <x:c r="B16" s="45" t="str">
+        <x:v>ESAS</x:v>
+      </x:c>
+      <x:c r="C16" s="45" t="str">
+        <x:v>Cycle court</x:v>
+      </x:c>
+      <x:c r="D16" s="45" t="str">
+        <x:v>Technicien supérieur aéronautique</x:v>
+      </x:c>
+      <x:c r="E16" s="45" t="str">
+        <x:v>https://www.inphb.ci/</x:v>
+      </x:c>
+      <x:c r="F16" s="45" t="str">
+        <x:v>Site officiel INP-HB</x:v>
+      </x:c>
+      <x:c r="G16" s="46" t="str">
+        <x:v>Aucune fiche publique stable et spécifique n'a été identifiée ; lien vers le site officiel.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/parametres_simulateur_inphb.xlsx
+++ b/parametres_simulateur_inphb.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
@@ -777,7 +777,7 @@
     <t xml:space="preserve">Gestion appliquée aux entreprises</t>
   </si>
   <si>
-    <t xml:space="preserve">https://escae.inphb.ci/public/formations</t>
+    <t xml:space="preserve">https://escae.inphb.ci/public/formations/cycle-technicien-superieur</t>
   </si>
   <si>
     <t xml:space="preserve">Page de l'école</t>
@@ -798,7 +798,7 @@
     <t xml:space="preserve">Économique et commerciale générale</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.inphb.ci/static/media/CPGE.9b4d786a11dd59ac7ac1.pdf</t>
+    <t xml:space="preserve">https://inphb.edu.ci/nos-ecoles/cpge/filieres/</t>
   </si>
   <si>
     <t xml:space="preserve">Plaquette officielle</t>
@@ -864,7 +864,7 @@
     <t xml:space="preserve">Procédés et maîtrise de l'énergie</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.inphb.ci/</t>
+    <t xml:space="preserve">https://inphb.edu.ci/nos-ecoles/</t>
   </si>
   <si>
     <t xml:space="preserve">Site officiel INP-HB</t>
@@ -883,27 +883,23 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* \-??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* \-??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;- &quot;_€_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;- &quot;_€_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0.00&quot; €&quot;_-;\-* #,##0.00&quot; €&quot;_-;_-* \-??&quot; €&quot;_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0.00&quot; €&quot;_-;\-* #,##0.00&quot; €&quot;_-;_-* \-??&quot; €&quot;_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0&quot; €&quot;_-;\-* #,##0&quot; €&quot;_-;_-* &quot;- €&quot;_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0&quot; €&quot;_-;\-* #,##0&quot; €&quot;_-;_-* &quot;- €&quot;_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="0\ %"/>
-    <numFmt numFmtId="174" formatCode="0\ %"/>
-    <numFmt numFmtId="175" formatCode="General"/>
-    <numFmt numFmtId="176" formatCode="0.00\ %"/>
-    <numFmt numFmtId="177" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;- &quot;_€_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00&quot; €&quot;_-;\-* #,##0.00&quot; €&quot;_-;_-* \-??&quot; €&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0&quot; €&quot;_-;\-* #,##0&quot; €&quot;_-;_-* &quot;- €&quot;_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="0\ %"/>
+    <numFmt numFmtId="170" formatCode="General"/>
+    <numFmt numFmtId="171" formatCode="0.00\ %"/>
+    <numFmt numFmtId="172" formatCode="0.00"/>
   </numFmts>
   <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1052,14 +1048,30 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1068,91 +1080,99 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="29" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="29" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="29" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="29" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="28" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="28" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2392,23 +2412,23 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="39.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>40</v>
       </c>
       <c r="F1" s="3"/>
@@ -4531,3831 +4551,3831 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="68.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="9" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="10" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="H1" s="8"/>
+      <c r="H1" s="9"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="11" t="n">
+      <c r="E2" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="11"/>
+      <c r="G5" s="12"/>
       <c r="H5" s="3"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="12"/>
       <c r="H6" s="3"/>
       <c r="I6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G7" s="11"/>
+      <c r="G7" s="12"/>
       <c r="H7" s="3"/>
       <c r="I7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G12" s="11"/>
+      <c r="G12" s="12"/>
       <c r="H12" s="3"/>
       <c r="I12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G13" s="11"/>
+      <c r="G13" s="12"/>
       <c r="H13" s="3"/>
       <c r="I13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G14" s="11"/>
+      <c r="G14" s="12"/>
       <c r="H14" s="3"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G15" s="11"/>
+      <c r="G15" s="12"/>
       <c r="H15" s="3"/>
       <c r="I15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="12" t="s">
         <v>129</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="12" t="s">
         <v>129</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="12" t="s">
         <v>129</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="12" t="s">
         <v>129</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="12" t="s">
         <v>129</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>129</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="12" t="s">
         <v>129</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="12" t="s">
         <v>129</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="12" t="s">
         <v>129</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="12" t="s">
         <v>129</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G29" s="11"/>
+      <c r="G29" s="12"/>
       <c r="H29" s="3"/>
       <c r="I29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E30" s="11" t="n">
+      <c r="E30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G30" s="11"/>
+      <c r="G30" s="12"/>
       <c r="H30" s="3"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G31" s="11"/>
+      <c r="G31" s="12"/>
       <c r="H31" s="3"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="E32" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G32" s="11"/>
+      <c r="G32" s="12"/>
       <c r="H32" s="3"/>
       <c r="I32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G33" s="11"/>
+      <c r="G33" s="12"/>
       <c r="H33" s="3"/>
       <c r="I33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G34" s="11"/>
+      <c r="G34" s="12"/>
       <c r="H34" s="3"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G35" s="11"/>
+      <c r="G35" s="12"/>
       <c r="H35" s="3"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G36" s="11"/>
+      <c r="G36" s="12"/>
       <c r="H36" s="3"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G37" s="11"/>
+      <c r="G37" s="12"/>
       <c r="H37" s="3"/>
       <c r="I37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G38" s="11"/>
+      <c r="G38" s="12"/>
       <c r="H38" s="3"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G39" s="11"/>
+      <c r="G39" s="12"/>
       <c r="H39" s="3"/>
       <c r="I39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G40" s="11"/>
+      <c r="G40" s="12"/>
       <c r="H40" s="3"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="G41" s="11" t="s">
+      <c r="G41" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C42" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="G42" s="11" t="s">
+      <c r="G42" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="G43" s="11" t="s">
+      <c r="G43" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D44" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E44" s="11" t="n">
+      <c r="E44" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="G44" s="11" t="s">
+      <c r="G44" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="11" t="n">
+      <c r="E45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G45" s="11"/>
+      <c r="G45" s="12"/>
       <c r="H45" s="3"/>
       <c r="I45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G46" s="11"/>
+      <c r="G46" s="12"/>
       <c r="H46" s="3"/>
       <c r="I46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E47" s="11" t="n">
+      <c r="E47" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G47" s="11"/>
+      <c r="G47" s="12"/>
       <c r="H47" s="3"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E48" s="11" t="n">
+      <c r="E48" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G48" s="11"/>
+      <c r="G48" s="12"/>
       <c r="H48" s="3"/>
       <c r="I48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E49" s="11" t="n">
+      <c r="E49" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G49" s="11"/>
+      <c r="G49" s="12"/>
       <c r="H49" s="3"/>
       <c r="I49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D50" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E50" s="11" t="n">
+      <c r="E50" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G50" s="11"/>
+      <c r="G50" s="12"/>
       <c r="H50" s="3"/>
       <c r="I50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E51" s="11" t="n">
+      <c r="E51" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G51" s="11"/>
+      <c r="G51" s="12"/>
       <c r="H51" s="3"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E52" s="11" t="n">
+      <c r="E52" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G52" s="11"/>
+      <c r="G52" s="12"/>
       <c r="H52" s="3"/>
       <c r="I52" s="1"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E53" s="11" t="n">
+      <c r="E53" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G53" s="11"/>
+      <c r="G53" s="12"/>
       <c r="H53" s="3"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E54" s="11" t="n">
+      <c r="E54" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G54" s="11"/>
+      <c r="G54" s="12"/>
       <c r="H54" s="3"/>
       <c r="I54" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E55" s="11" t="n">
+      <c r="E55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G55" s="11"/>
+      <c r="G55" s="12"/>
       <c r="H55" s="3"/>
       <c r="I55" s="1"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E56" s="11" t="n">
+      <c r="E56" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G56" s="11"/>
+      <c r="G56" s="12"/>
       <c r="H56" s="3"/>
       <c r="I56" s="1"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E57" s="11" t="n">
+      <c r="E57" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G57" s="11"/>
+      <c r="G57" s="12"/>
       <c r="H57" s="3"/>
       <c r="I57" s="1"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C58" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D58" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E58" s="11" t="n">
+      <c r="E58" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G58" s="11"/>
+      <c r="G58" s="12"/>
       <c r="H58" s="3"/>
       <c r="I58" s="1"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D59" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E59" s="11" t="n">
+      <c r="E59" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G59" s="11"/>
+      <c r="G59" s="12"/>
       <c r="H59" s="3"/>
       <c r="I59" s="1"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C60" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D60" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E60" s="11" t="n">
+      <c r="E60" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="G60" s="11"/>
+      <c r="G60" s="12"/>
       <c r="H60" s="3"/>
       <c r="I60" s="1"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D61" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="E61" s="11" t="n">
+      <c r="E61" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="G61" s="11"/>
+      <c r="G61" s="12"/>
       <c r="H61" s="3"/>
       <c r="I61" s="1"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D62" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E62" s="11" t="n">
+      <c r="E62" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="G62" s="11"/>
+      <c r="G62" s="12"/>
       <c r="H62" s="3"/>
       <c r="I62" s="1"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C63" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D63" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E63" s="11" t="n">
+      <c r="E63" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="G63" s="11"/>
+      <c r="G63" s="12"/>
       <c r="H63" s="3"/>
       <c r="I63" s="1"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D64" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="E64" s="11" t="n">
+      <c r="E64" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="G64" s="11"/>
+      <c r="G64" s="12"/>
       <c r="H64" s="3"/>
       <c r="I64" s="1"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D65" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E65" s="11" t="n">
+      <c r="E65" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="G65" s="11"/>
+      <c r="G65" s="12"/>
       <c r="H65" s="3"/>
       <c r="I65" s="1"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E66" s="11" t="n">
+      <c r="E66" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="G66" s="11"/>
+      <c r="G66" s="12"/>
       <c r="H66" s="3"/>
       <c r="I66" s="1"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B67" s="12" t="s">
+      <c r="B67" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="E67" s="12" t="n">
+      <c r="E67" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F67" s="12" t="s">
+      <c r="F67" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G67" s="12"/>
+      <c r="G67" s="13"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="E68" s="12" t="n">
+      <c r="E68" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F68" s="12" t="s">
+      <c r="F68" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G68" s="12"/>
+      <c r="G68" s="13"/>
       <c r="I68" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="12" t="s">
+      <c r="A69" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B69" s="12" t="s">
+      <c r="B69" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="C69" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="D69" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E69" s="12" t="n">
+      <c r="E69" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F69" s="12" t="s">
+      <c r="F69" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G69" s="12"/>
+      <c r="G69" s="13"/>
       <c r="I69" s="1"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12" t="s">
+      <c r="A70" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D70" s="12" t="s">
+      <c r="D70" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="E70" s="12" t="n">
+      <c r="E70" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F70" s="12" t="s">
+      <c r="F70" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G70" s="12"/>
+      <c r="G70" s="13"/>
       <c r="I70" s="1"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="12" t="s">
+      <c r="A71" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="E71" s="12" t="n">
+      <c r="E71" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F71" s="12" t="s">
+      <c r="F71" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G71" s="12"/>
+      <c r="G71" s="13"/>
       <c r="I71" s="1"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="12" t="s">
+      <c r="A72" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D72" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E72" s="12" t="n">
+      <c r="E72" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F72" s="12" t="s">
+      <c r="F72" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G72" s="12"/>
+      <c r="G72" s="13"/>
       <c r="I72" s="1"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="12" t="s">
+      <c r="A73" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B73" s="12" t="s">
+      <c r="B73" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D73" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="E73" s="12" t="n">
+      <c r="E73" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F73" s="12" t="s">
+      <c r="F73" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G73" s="12"/>
+      <c r="G73" s="13"/>
       <c r="I73" s="1"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12" t="s">
+      <c r="A74" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D74" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="E74" s="12" t="n">
+      <c r="E74" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F74" s="12" t="s">
+      <c r="F74" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G74" s="12"/>
+      <c r="G74" s="13"/>
       <c r="I74" s="1"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="11" t="s">
+      <c r="A75" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C75" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E75" s="11" t="n">
+      <c r="E75" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F75" s="11" t="s">
+      <c r="F75" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G75" s="11" t="s">
+      <c r="G75" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="1"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D76" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E76" s="11" t="n">
+      <c r="E76" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G76" s="11" t="s">
+      <c r="G76" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="1"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="D77" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E77" s="11" t="n">
+      <c r="E77" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F77" s="11" t="s">
+      <c r="F77" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G77" s="11" t="s">
+      <c r="G77" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="1"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C78" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D78" s="11" t="s">
+      <c r="D78" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E78" s="11" t="n">
+      <c r="E78" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F78" s="11" t="s">
+      <c r="F78" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="G78" s="11" t="s">
+      <c r="G78" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="1"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="11" t="s">
+      <c r="A79" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C79" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D79" s="11" t="s">
+      <c r="D79" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E79" s="11" t="n">
+      <c r="E79" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F79" s="11" t="s">
+      <c r="F79" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G79" s="11" t="s">
+      <c r="G79" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="1"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="11" t="s">
+      <c r="A80" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C80" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D80" s="11" t="s">
+      <c r="D80" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E80" s="11" t="n">
+      <c r="E80" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F80" s="11" t="s">
+      <c r="F80" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G80" s="11" t="s">
+      <c r="G80" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H80" s="3"/>
       <c r="I80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="11" t="s">
+      <c r="A81" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C81" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D81" s="11" t="s">
+      <c r="D81" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E81" s="11" t="n">
+      <c r="E81" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F81" s="11" t="s">
+      <c r="F81" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G81" s="11" t="s">
+      <c r="G81" s="12" t="s">
         <v>122</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="1"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="12" t="s">
+      <c r="A82" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E82" s="12" t="n">
+      <c r="E82" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F82" s="12" t="s">
+      <c r="F82" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G82" s="12" t="s">
+      <c r="G82" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I82" s="1"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="12" t="s">
+      <c r="A83" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B83" s="12" t="s">
+      <c r="B83" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C83" s="12" t="s">
+      <c r="C83" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E83" s="12" t="n">
+      <c r="E83" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="12" t="s">
+      <c r="F83" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G83" s="12" t="s">
+      <c r="G83" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I83" s="1"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="12" t="s">
+      <c r="A84" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B84" s="12" t="s">
+      <c r="B84" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E84" s="12" t="n">
+      <c r="E84" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F84" s="12" t="s">
+      <c r="F84" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G84" s="12" t="s">
+      <c r="G84" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I84" s="1"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="12" t="s">
+      <c r="A85" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B85" s="12" t="s">
+      <c r="B85" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="D85" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E85" s="12" t="n">
+      <c r="E85" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F85" s="12" t="s">
+      <c r="F85" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G85" s="12" t="s">
+      <c r="G85" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I85" s="1"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="12" t="s">
+      <c r="A86" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="B86" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C86" s="12" t="s">
+      <c r="C86" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E86" s="12" t="n">
+      <c r="E86" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F86" s="12" t="s">
+      <c r="F86" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G86" s="12" t="s">
+      <c r="G86" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I86" s="1"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="12" t="s">
+      <c r="A87" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B87" s="12" t="s">
+      <c r="B87" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C87" s="12" t="s">
+      <c r="C87" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E87" s="12" t="n">
+      <c r="E87" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F87" s="12" t="s">
+      <c r="F87" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G87" s="12" t="s">
+      <c r="G87" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I87" s="1"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="12" t="s">
+      <c r="A88" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C88" s="12" t="s">
+      <c r="C88" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D88" s="12" t="s">
+      <c r="D88" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E88" s="12" t="n">
+      <c r="E88" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F88" s="12" t="s">
+      <c r="F88" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G88" s="12" t="s">
+      <c r="G88" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I88" s="1"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="12" t="s">
+      <c r="A89" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B89" s="12" t="s">
+      <c r="B89" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C89" s="12" t="s">
+      <c r="C89" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D89" s="12" t="s">
+      <c r="D89" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E89" s="12" t="n">
+      <c r="E89" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F89" s="12" t="s">
+      <c r="F89" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G89" s="12" t="s">
+      <c r="G89" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I89" s="1"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="12" t="s">
+      <c r="A90" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E90" s="12" t="n">
+      <c r="E90" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F90" s="12" t="s">
+      <c r="F90" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G90" s="12" t="s">
+      <c r="G90" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I90" s="1"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="12" t="s">
+      <c r="A91" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B91" s="12" t="s">
+      <c r="B91" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C91" s="12" t="s">
+      <c r="C91" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D91" s="12" t="s">
+      <c r="D91" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E91" s="12" t="n">
+      <c r="E91" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F91" s="12" t="s">
+      <c r="F91" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G91" s="12" t="s">
+      <c r="G91" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I91" s="1"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="12" t="s">
+      <c r="A92" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C92" s="12" t="s">
+      <c r="C92" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D92" s="12" t="s">
+      <c r="D92" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E92" s="12" t="n">
+      <c r="E92" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F92" s="12" t="s">
+      <c r="F92" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G92" s="12" t="s">
+      <c r="G92" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I92" s="1"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="12" t="s">
+      <c r="A93" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D93" s="12" t="s">
+      <c r="D93" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E93" s="12" t="n">
+      <c r="E93" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F93" s="12" t="s">
+      <c r="F93" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G93" s="12" t="s">
+      <c r="G93" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I93" s="1"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="12" t="s">
+      <c r="A94" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C94" s="12" t="s">
+      <c r="C94" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D94" s="12" t="s">
+      <c r="D94" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E94" s="12" t="n">
+      <c r="E94" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F94" s="12" t="s">
+      <c r="F94" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G94" s="12" t="s">
+      <c r="G94" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I94" s="1"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="12" t="s">
+      <c r="A95" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B95" s="12" t="s">
+      <c r="B95" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C95" s="12" t="s">
+      <c r="C95" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D95" s="12" t="s">
+      <c r="D95" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E95" s="12" t="n">
+      <c r="E95" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F95" s="12" t="s">
+      <c r="F95" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G95" s="12" t="s">
+      <c r="G95" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I95" s="1"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="12" t="s">
+      <c r="A96" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C96" s="12" t="s">
+      <c r="C96" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D96" s="12" t="s">
+      <c r="D96" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E96" s="12" t="n">
+      <c r="E96" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F96" s="12" t="s">
+      <c r="F96" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G96" s="12" t="s">
+      <c r="G96" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I96" s="1"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="12" t="s">
+      <c r="A97" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B97" s="12" t="s">
+      <c r="B97" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C97" s="12" t="s">
+      <c r="C97" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D97" s="12" t="s">
+      <c r="D97" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E97" s="12" t="n">
+      <c r="E97" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F97" s="12" t="s">
+      <c r="F97" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G97" s="12" t="s">
+      <c r="G97" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I97" s="1"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="12" t="s">
+      <c r="A98" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B98" s="12" t="s">
+      <c r="B98" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C98" s="12" t="s">
+      <c r="C98" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D98" s="12" t="s">
+      <c r="D98" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E98" s="12" t="n">
+      <c r="E98" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F98" s="12" t="s">
+      <c r="F98" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G98" s="12" t="s">
+      <c r="G98" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I98" s="1"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="12" t="s">
+      <c r="A99" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B99" s="12" t="s">
+      <c r="B99" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C99" s="12" t="s">
+      <c r="C99" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D99" s="12" t="s">
+      <c r="D99" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E99" s="12" t="n">
+      <c r="E99" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F99" s="12" t="s">
+      <c r="F99" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G99" s="12" t="s">
+      <c r="G99" s="13" t="s">
         <v>153</v>
       </c>
       <c r="I99" s="1"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="12" t="s">
+      <c r="A100" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C100" s="12" t="s">
+      <c r="C100" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D100" s="12" t="s">
+      <c r="D100" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E100" s="12" t="n">
+      <c r="E100" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F100" s="12" t="s">
+      <c r="F100" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G100" s="12" t="s">
+      <c r="G100" s="13" t="s">
         <v>157</v>
       </c>
       <c r="I100" s="1"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="12" t="s">
+      <c r="A101" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B101" s="12" t="s">
+      <c r="B101" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C101" s="12" t="s">
+      <c r="C101" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D101" s="12" t="s">
+      <c r="D101" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E101" s="12" t="n">
+      <c r="E101" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F101" s="12" t="s">
+      <c r="F101" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G101" s="12" t="s">
+      <c r="G101" s="13" t="s">
         <v>157</v>
       </c>
       <c r="I101" s="1"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="12" t="s">
+      <c r="A102" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B102" s="12" t="s">
+      <c r="B102" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C102" s="12" t="s">
+      <c r="C102" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D102" s="12" t="s">
+      <c r="D102" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E102" s="12" t="n">
+      <c r="E102" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F102" s="12" t="s">
+      <c r="F102" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G102" s="12" t="s">
+      <c r="G102" s="13" t="s">
         <v>157</v>
       </c>
       <c r="I102" s="1"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="12" t="s">
+      <c r="A103" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B103" s="12" t="s">
+      <c r="B103" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C103" s="12" t="s">
+      <c r="C103" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D103" s="12" t="s">
+      <c r="D103" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E103" s="12" t="n">
+      <c r="E103" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F103" s="12" t="s">
+      <c r="F103" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G103" s="12" t="s">
+      <c r="G103" s="13" t="s">
         <v>157</v>
       </c>
       <c r="I103" s="1"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="12" t="s">
+      <c r="A104" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B104" s="12" t="s">
+      <c r="B104" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C104" s="12" t="s">
+      <c r="C104" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D104" s="12" t="s">
+      <c r="D104" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E104" s="12" t="n">
+      <c r="E104" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F104" s="12" t="s">
+      <c r="F104" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G104" s="12" t="s">
+      <c r="G104" s="13" t="s">
         <v>157</v>
       </c>
       <c r="I104" s="1"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="12" t="s">
+      <c r="A105" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B105" s="12" t="s">
+      <c r="B105" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C105" s="12" t="s">
+      <c r="C105" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D105" s="12" t="s">
+      <c r="D105" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E105" s="12" t="n">
+      <c r="E105" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F105" s="12" t="s">
+      <c r="F105" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G105" s="12" t="s">
+      <c r="G105" s="13" t="s">
         <v>157</v>
       </c>
       <c r="I105" s="1"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="12" t="s">
+      <c r="A106" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B106" s="12" t="s">
+      <c r="B106" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C106" s="12" t="s">
+      <c r="C106" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D106" s="12" t="s">
+      <c r="D106" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E106" s="12" t="n">
+      <c r="E106" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F106" s="12" t="s">
+      <c r="F106" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G106" s="12" t="s">
+      <c r="G106" s="13" t="s">
         <v>157</v>
       </c>
       <c r="I106" s="1"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="12" t="s">
+      <c r="A107" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B107" s="12" t="s">
+      <c r="B107" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C107" s="12" t="s">
+      <c r="C107" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D107" s="12" t="s">
+      <c r="D107" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E107" s="12" t="n">
+      <c r="E107" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F107" s="12" t="s">
+      <c r="F107" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G107" s="12" t="s">
+      <c r="G107" s="13" t="s">
         <v>157</v>
       </c>
       <c r="I107" s="1"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="12" t="s">
+      <c r="A108" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B108" s="12" t="s">
+      <c r="B108" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C108" s="12" t="s">
+      <c r="C108" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D108" s="12" t="s">
+      <c r="D108" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E108" s="12" t="n">
+      <c r="E108" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F108" s="12" t="s">
+      <c r="F108" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G108" s="12" t="s">
+      <c r="G108" s="13" t="s">
         <v>157</v>
       </c>
       <c r="I108" s="1"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="12" t="s">
+      <c r="A109" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B109" s="12" t="s">
+      <c r="B109" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C109" s="12" t="s">
+      <c r="C109" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D109" s="12" t="s">
+      <c r="D109" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E109" s="12" t="n">
+      <c r="E109" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F109" s="12" t="s">
+      <c r="F109" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G109" s="12" t="s">
+      <c r="G109" s="13" t="s">
         <v>159</v>
       </c>
       <c r="I109" s="1"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="12" t="s">
+      <c r="A110" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B110" s="12" t="s">
+      <c r="B110" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C110" s="12" t="s">
+      <c r="C110" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D110" s="12" t="s">
+      <c r="D110" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E110" s="12" t="n">
+      <c r="E110" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F110" s="12" t="s">
+      <c r="F110" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G110" s="12" t="s">
+      <c r="G110" s="13" t="s">
         <v>159</v>
       </c>
       <c r="I110" s="1"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="12" t="s">
+      <c r="A111" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B111" s="12" t="s">
+      <c r="B111" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C111" s="12" t="s">
+      <c r="C111" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D111" s="12" t="s">
+      <c r="D111" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E111" s="12" t="n">
+      <c r="E111" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F111" s="12" t="s">
+      <c r="F111" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G111" s="12" t="s">
+      <c r="G111" s="13" t="s">
         <v>159</v>
       </c>
       <c r="I111" s="1"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="12" t="s">
+      <c r="A112" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B112" s="12" t="s">
+      <c r="B112" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C112" s="12" t="s">
+      <c r="C112" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D112" s="12" t="s">
+      <c r="D112" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E112" s="12" t="n">
+      <c r="E112" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F112" s="12" t="s">
+      <c r="F112" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G112" s="12" t="s">
+      <c r="G112" s="13" t="s">
         <v>159</v>
       </c>
       <c r="I112" s="1"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="12" t="s">
+      <c r="A113" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B113" s="12" t="s">
+      <c r="B113" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C113" s="12" t="s">
+      <c r="C113" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D113" s="12" t="s">
+      <c r="D113" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E113" s="12" t="n">
+      <c r="E113" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F113" s="12" t="s">
+      <c r="F113" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G113" s="12" t="s">
+      <c r="G113" s="13" t="s">
         <v>159</v>
       </c>
       <c r="I113" s="1"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="12" t="s">
+      <c r="A114" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B114" s="12" t="s">
+      <c r="B114" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C114" s="12" t="s">
+      <c r="C114" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D114" s="12" t="s">
+      <c r="D114" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E114" s="12" t="n">
+      <c r="E114" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F114" s="12" t="s">
+      <c r="F114" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G114" s="12" t="s">
+      <c r="G114" s="13" t="s">
         <v>159</v>
       </c>
       <c r="I114" s="1"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="12" t="s">
+      <c r="A115" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B115" s="12" t="s">
+      <c r="B115" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C115" s="12" t="s">
+      <c r="C115" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D115" s="12" t="s">
+      <c r="D115" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E115" s="12" t="n">
+      <c r="E115" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F115" s="12" t="s">
+      <c r="F115" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G115" s="12" t="s">
+      <c r="G115" s="13" t="s">
         <v>159</v>
       </c>
       <c r="I115" s="1"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="12" t="s">
+      <c r="A116" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B116" s="12" t="s">
+      <c r="B116" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C116" s="12" t="s">
+      <c r="C116" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D116" s="12" t="s">
+      <c r="D116" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E116" s="12" t="n">
+      <c r="E116" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F116" s="12" t="s">
+      <c r="F116" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G116" s="12" t="s">
+      <c r="G116" s="13" t="s">
         <v>159</v>
       </c>
       <c r="I116" s="1"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="12" t="s">
+      <c r="A117" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B117" s="12" t="s">
+      <c r="B117" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C117" s="12" t="s">
+      <c r="C117" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D117" s="12" t="s">
+      <c r="D117" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E117" s="12" t="n">
+      <c r="E117" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F117" s="12" t="s">
+      <c r="F117" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G117" s="12" t="s">
+      <c r="G117" s="13" t="s">
         <v>159</v>
       </c>
       <c r="I117" s="1"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="12" t="s">
+      <c r="A118" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B118" s="12" t="s">
+      <c r="B118" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C118" s="12" t="s">
+      <c r="C118" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D118" s="12" t="s">
+      <c r="D118" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E118" s="12" t="n">
+      <c r="E118" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F118" s="12" t="s">
+      <c r="F118" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G118" s="12" t="s">
+      <c r="G118" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I118" s="1"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="12" t="s">
+      <c r="A119" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B119" s="12" t="s">
+      <c r="B119" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C119" s="12" t="s">
+      <c r="C119" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D119" s="12" t="s">
+      <c r="D119" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E119" s="12" t="n">
+      <c r="E119" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F119" s="12" t="s">
+      <c r="F119" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G119" s="12" t="s">
+      <c r="G119" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I119" s="1"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="12" t="s">
+      <c r="A120" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B120" s="12" t="s">
+      <c r="B120" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C120" s="12" t="s">
+      <c r="C120" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D120" s="12" t="s">
+      <c r="D120" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E120" s="12" t="n">
+      <c r="E120" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F120" s="12" t="s">
+      <c r="F120" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G120" s="12" t="s">
+      <c r="G120" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I120" s="1"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="12" t="s">
+      <c r="A121" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B121" s="12" t="s">
+      <c r="B121" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C121" s="12" t="s">
+      <c r="C121" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D121" s="12" t="s">
+      <c r="D121" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E121" s="12" t="n">
+      <c r="E121" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F121" s="12" t="s">
+      <c r="F121" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G121" s="12" t="s">
+      <c r="G121" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I121" s="1"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="12" t="s">
+      <c r="A122" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B122" s="12" t="s">
+      <c r="B122" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C122" s="12" t="s">
+      <c r="C122" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D122" s="12" t="s">
+      <c r="D122" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E122" s="12" t="n">
+      <c r="E122" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F122" s="12" t="s">
+      <c r="F122" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G122" s="12" t="s">
+      <c r="G122" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I122" s="1"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="12" t="s">
+      <c r="A123" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B123" s="12" t="s">
+      <c r="B123" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C123" s="12" t="s">
+      <c r="C123" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D123" s="12" t="s">
+      <c r="D123" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E123" s="12" t="n">
+      <c r="E123" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F123" s="12" t="s">
+      <c r="F123" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G123" s="12" t="s">
+      <c r="G123" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I123" s="1"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="12" t="s">
+      <c r="A124" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B124" s="12" t="s">
+      <c r="B124" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C124" s="12" t="s">
+      <c r="C124" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D124" s="12" t="s">
+      <c r="D124" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E124" s="12" t="n">
+      <c r="E124" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F124" s="12" t="s">
+      <c r="F124" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G124" s="12" t="s">
+      <c r="G124" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I124" s="1"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="12" t="s">
+      <c r="A125" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B125" s="12" t="s">
+      <c r="B125" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C125" s="12" t="s">
+      <c r="C125" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D125" s="12" t="s">
+      <c r="D125" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E125" s="12" t="n">
+      <c r="E125" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F125" s="12" t="s">
+      <c r="F125" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G125" s="12" t="s">
+      <c r="G125" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I125" s="1"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="12" t="s">
+      <c r="A126" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B126" s="12" t="s">
+      <c r="B126" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C126" s="12" t="s">
+      <c r="C126" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D126" s="12" t="s">
+      <c r="D126" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E126" s="12" t="n">
+      <c r="E126" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F126" s="12" t="s">
+      <c r="F126" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G126" s="12" t="s">
+      <c r="G126" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I126" s="1"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="12" t="s">
+      <c r="A127" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B127" s="12" t="s">
+      <c r="B127" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C127" s="12" t="s">
+      <c r="C127" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D127" s="12" t="s">
+      <c r="D127" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E127" s="12" t="n">
+      <c r="E127" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F127" s="12" t="s">
+      <c r="F127" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G127" s="12" t="s">
+      <c r="G127" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I127" s="1"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="12" t="s">
+      <c r="A128" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B128" s="12" t="s">
+      <c r="B128" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C128" s="12" t="s">
+      <c r="C128" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D128" s="12" t="s">
+      <c r="D128" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E128" s="12" t="n">
+      <c r="E128" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F128" s="12" t="s">
+      <c r="F128" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G128" s="12" t="s">
+      <c r="G128" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I128" s="1"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="12" t="s">
+      <c r="A129" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B129" s="12" t="s">
+      <c r="B129" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C129" s="12" t="s">
+      <c r="C129" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D129" s="12" t="s">
+      <c r="D129" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E129" s="12" t="n">
+      <c r="E129" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F129" s="12" t="s">
+      <c r="F129" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G129" s="12" t="s">
+      <c r="G129" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I129" s="1"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="12" t="s">
+      <c r="A130" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B130" s="12" t="s">
+      <c r="B130" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C130" s="12" t="s">
+      <c r="C130" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D130" s="12" t="s">
+      <c r="D130" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E130" s="12" t="n">
+      <c r="E130" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F130" s="12" t="s">
+      <c r="F130" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G130" s="12" t="s">
+      <c r="G130" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I130" s="1"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="12" t="s">
+      <c r="A131" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B131" s="12" t="s">
+      <c r="B131" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C131" s="12" t="s">
+      <c r="C131" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D131" s="12" t="s">
+      <c r="D131" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E131" s="12" t="n">
+      <c r="E131" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F131" s="12" t="s">
+      <c r="F131" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G131" s="12" t="s">
+      <c r="G131" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I131" s="1"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="12" t="s">
+      <c r="A132" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B132" s="12" t="s">
+      <c r="B132" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C132" s="12" t="s">
+      <c r="C132" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D132" s="12" t="s">
+      <c r="D132" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E132" s="12" t="n">
+      <c r="E132" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F132" s="12" t="s">
+      <c r="F132" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G132" s="12" t="s">
+      <c r="G132" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I132" s="1"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="12" t="s">
+      <c r="A133" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B133" s="12" t="s">
+      <c r="B133" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C133" s="12" t="s">
+      <c r="C133" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D133" s="12" t="s">
+      <c r="D133" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E133" s="12" t="n">
+      <c r="E133" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F133" s="12" t="s">
+      <c r="F133" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G133" s="12" t="s">
+      <c r="G133" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I133" s="1"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="12" t="s">
+      <c r="A134" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B134" s="12" t="s">
+      <c r="B134" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C134" s="12" t="s">
+      <c r="C134" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D134" s="12" t="s">
+      <c r="D134" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E134" s="12" t="n">
+      <c r="E134" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F134" s="12" t="s">
+      <c r="F134" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G134" s="12" t="s">
+      <c r="G134" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I134" s="1"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="12" t="s">
+      <c r="A135" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B135" s="12" t="s">
+      <c r="B135" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C135" s="12" t="s">
+      <c r="C135" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="D135" s="12" t="s">
+      <c r="D135" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E135" s="12" t="n">
+      <c r="E135" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F135" s="12" t="s">
+      <c r="F135" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G135" s="12" t="s">
+      <c r="G135" s="13" t="s">
         <v>161</v>
       </c>
       <c r="I135" s="1"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="12" t="s">
+      <c r="A136" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B136" s="12" t="s">
+      <c r="B136" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C136" s="12" t="s">
+      <c r="C136" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D136" s="12" t="s">
+      <c r="D136" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E136" s="12" t="n">
+      <c r="E136" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F136" s="12" t="s">
+      <c r="F136" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G136" s="12" t="s">
+      <c r="G136" s="13" t="s">
         <v>164</v>
       </c>
       <c r="I136" s="1"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="12" t="s">
+      <c r="A137" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B137" s="12" t="s">
+      <c r="B137" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C137" s="12" t="s">
+      <c r="C137" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D137" s="12" t="s">
+      <c r="D137" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E137" s="12" t="n">
+      <c r="E137" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F137" s="12" t="s">
+      <c r="F137" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G137" s="12" t="s">
+      <c r="G137" s="13" t="s">
         <v>164</v>
       </c>
       <c r="I137" s="1"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="12" t="s">
+      <c r="A138" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B138" s="12" t="s">
+      <c r="B138" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C138" s="12" t="s">
+      <c r="C138" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D138" s="12" t="s">
+      <c r="D138" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E138" s="12" t="n">
+      <c r="E138" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F138" s="12" t="s">
+      <c r="F138" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G138" s="12" t="s">
+      <c r="G138" s="13" t="s">
         <v>164</v>
       </c>
       <c r="I138" s="1"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="12" t="s">
+      <c r="A139" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B139" s="12" t="s">
+      <c r="B139" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C139" s="12" t="s">
+      <c r="C139" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D139" s="12" t="s">
+      <c r="D139" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E139" s="12" t="n">
+      <c r="E139" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F139" s="12" t="s">
+      <c r="F139" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G139" s="12" t="s">
+      <c r="G139" s="13" t="s">
         <v>164</v>
       </c>
       <c r="I139" s="1"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="12" t="s">
+      <c r="A140" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B140" s="12" t="s">
+      <c r="B140" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C140" s="12" t="s">
+      <c r="C140" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="D140" s="12" t="s">
+      <c r="D140" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E140" s="12" t="n">
+      <c r="E140" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F140" s="12" t="s">
+      <c r="F140" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G140" s="12" t="s">
+      <c r="G140" s="13" t="s">
         <v>164</v>
       </c>
       <c r="I140" s="1"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="12" t="s">
+      <c r="A141" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B141" s="12" t="s">
+      <c r="B141" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C141" s="12" t="s">
+      <c r="C141" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="D141" s="12" t="s">
+      <c r="D141" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E141" s="12" t="n">
+      <c r="E141" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F141" s="12" t="s">
+      <c r="F141" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G141" s="12" t="s">
+      <c r="G141" s="13" t="s">
         <v>164</v>
       </c>
       <c r="I141" s="1"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="12" t="s">
+      <c r="A142" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B142" s="12" t="s">
+      <c r="B142" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C142" s="12" t="s">
+      <c r="C142" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="D142" s="12" t="s">
+      <c r="D142" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E142" s="12" t="n">
+      <c r="E142" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F142" s="12" t="s">
+      <c r="F142" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G142" s="12" t="s">
+      <c r="G142" s="13" t="s">
         <v>164</v>
       </c>
       <c r="I142" s="1"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="12" t="s">
+      <c r="A143" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B143" s="12" t="s">
+      <c r="B143" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C143" s="12" t="s">
+      <c r="C143" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="D143" s="12" t="s">
+      <c r="D143" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E143" s="12" t="n">
+      <c r="E143" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="F143" s="12" t="s">
+      <c r="F143" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G143" s="12" t="s">
+      <c r="G143" s="13" t="s">
         <v>164</v>
       </c>
       <c r="I143" s="1"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="12" t="s">
+      <c r="A144" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B144" s="12" t="s">
+      <c r="B144" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C144" s="12" t="s">
+      <c r="C144" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="D144" s="12" t="s">
+      <c r="D144" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="E144" s="12" t="n">
+      <c r="E144" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F144" s="12" t="s">
+      <c r="F144" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="G144" s="12" t="s">
+      <c r="G144" s="13" t="s">
         <v>164</v>
       </c>
       <c r="I144" s="1"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="12" t="s">
+      <c r="A145" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B145" s="12" t="s">
+      <c r="B145" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C145" s="12" t="s">
+      <c r="C145" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D145" s="12" t="s">
+      <c r="D145" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E145" s="12" t="n">
+      <c r="E145" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F145" s="12" t="s">
+      <c r="F145" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G145" s="12"/>
+      <c r="G145" s="13"/>
       <c r="I145" s="1"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="12" t="s">
+      <c r="A146" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B146" s="12" t="s">
+      <c r="B146" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C146" s="12" t="s">
+      <c r="C146" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D146" s="12" t="s">
+      <c r="D146" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E146" s="12" t="n">
+      <c r="E146" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F146" s="12" t="s">
+      <c r="F146" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G146" s="12"/>
+      <c r="G146" s="13"/>
       <c r="I146" s="1"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="12" t="s">
+      <c r="A147" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B147" s="12" t="s">
+      <c r="B147" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C147" s="12" t="s">
+      <c r="C147" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D147" s="12" t="s">
+      <c r="D147" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E147" s="12" t="n">
+      <c r="E147" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F147" s="12" t="s">
+      <c r="F147" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G147" s="12"/>
+      <c r="G147" s="13"/>
       <c r="I147" s="1"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="12" t="s">
+      <c r="A148" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B148" s="12" t="s">
+      <c r="B148" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C148" s="12" t="s">
+      <c r="C148" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D148" s="12" t="s">
+      <c r="D148" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E148" s="12" t="n">
+      <c r="E148" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F148" s="12" t="s">
+      <c r="F148" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G148" s="12"/>
+      <c r="G148" s="13"/>
       <c r="I148" s="1"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="12" t="s">
+      <c r="A149" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B149" s="12" t="s">
+      <c r="B149" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C149" s="12" t="s">
+      <c r="C149" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D149" s="12" t="s">
+      <c r="D149" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E149" s="12" t="n">
+      <c r="E149" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F149" s="12" t="s">
+      <c r="F149" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G149" s="12"/>
+      <c r="G149" s="13"/>
       <c r="I149" s="1"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="12" t="s">
+      <c r="A150" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B150" s="12" t="s">
+      <c r="B150" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C150" s="12" t="s">
+      <c r="C150" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D150" s="12" t="s">
+      <c r="D150" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="E150" s="12" t="n">
+      <c r="E150" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F150" s="12" t="s">
+      <c r="F150" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G150" s="12"/>
+      <c r="G150" s="13"/>
       <c r="I150" s="1"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="12" t="s">
+      <c r="A151" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B151" s="12" t="s">
+      <c r="B151" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C151" s="12" t="s">
+      <c r="C151" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D151" s="12" t="s">
+      <c r="D151" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="E151" s="12" t="n">
+      <c r="E151" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F151" s="12" t="s">
+      <c r="F151" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G151" s="12"/>
+      <c r="G151" s="13"/>
       <c r="I151" s="1"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="12" t="s">
+      <c r="A152" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B152" s="12" t="s">
+      <c r="B152" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C152" s="12" t="s">
+      <c r="C152" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D152" s="12" t="s">
+      <c r="D152" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E152" s="12" t="n">
+      <c r="E152" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F152" s="12" t="s">
+      <c r="F152" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G152" s="12"/>
+      <c r="G152" s="13"/>
       <c r="I152" s="1"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="12" t="s">
+      <c r="A153" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B153" s="12" t="s">
+      <c r="B153" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C153" s="12" t="s">
+      <c r="C153" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D153" s="12" t="s">
+      <c r="D153" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E153" s="12" t="n">
+      <c r="E153" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F153" s="12" t="s">
+      <c r="F153" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G153" s="12"/>
+      <c r="G153" s="13"/>
       <c r="I153" s="1"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="12" t="s">
+      <c r="A154" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B154" s="12" t="s">
+      <c r="B154" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C154" s="12" t="s">
+      <c r="C154" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D154" s="12" t="s">
+      <c r="D154" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E154" s="12" t="n">
+      <c r="E154" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F154" s="12" t="s">
+      <c r="F154" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G154" s="12"/>
+      <c r="G154" s="13"/>
       <c r="I154" s="1"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="12" t="s">
+      <c r="A155" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B155" s="12" t="s">
+      <c r="B155" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C155" s="12" t="s">
+      <c r="C155" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D155" s="12" t="s">
+      <c r="D155" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E155" s="12" t="n">
+      <c r="E155" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F155" s="12" t="s">
+      <c r="F155" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G155" s="12"/>
+      <c r="G155" s="13"/>
       <c r="I155" s="1"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="12" t="s">
+      <c r="A156" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B156" s="12" t="s">
+      <c r="B156" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C156" s="12" t="s">
+      <c r="C156" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D156" s="12" t="s">
+      <c r="D156" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E156" s="12" t="n">
+      <c r="E156" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F156" s="12" t="s">
+      <c r="F156" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G156" s="12"/>
+      <c r="G156" s="13"/>
       <c r="I156" s="1"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="12" t="s">
+      <c r="A157" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B157" s="12" t="s">
+      <c r="B157" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C157" s="12" t="s">
+      <c r="C157" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D157" s="12" t="s">
+      <c r="D157" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="E157" s="12" t="n">
+      <c r="E157" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F157" s="12" t="s">
+      <c r="F157" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G157" s="12"/>
+      <c r="G157" s="13"/>
       <c r="I157" s="1"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="12" t="s">
+      <c r="A158" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B158" s="12" t="s">
+      <c r="B158" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C158" s="12" t="s">
+      <c r="C158" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D158" s="12" t="s">
+      <c r="D158" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="E158" s="12" t="n">
+      <c r="E158" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F158" s="12" t="s">
+      <c r="F158" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G158" s="12"/>
+      <c r="G158" s="13"/>
       <c r="I158" s="1"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="12" t="s">
+      <c r="A159" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B159" s="12" t="s">
+      <c r="B159" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C159" s="12" t="s">
+      <c r="C159" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D159" s="12" t="s">
+      <c r="D159" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E159" s="12" t="n">
+      <c r="E159" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F159" s="12" t="s">
+      <c r="F159" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G159" s="12"/>
+      <c r="G159" s="13"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="12" t="s">
+      <c r="A160" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B160" s="12" t="s">
+      <c r="B160" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C160" s="12" t="s">
+      <c r="C160" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D160" s="12" t="s">
+      <c r="D160" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E160" s="12" t="n">
+      <c r="E160" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F160" s="12" t="s">
+      <c r="F160" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G160" s="12"/>
+      <c r="G160" s="13"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="12" t="s">
+      <c r="A161" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B161" s="12" t="s">
+      <c r="B161" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C161" s="12" t="s">
+      <c r="C161" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D161" s="12" t="s">
+      <c r="D161" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E161" s="12" t="n">
+      <c r="E161" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="F161" s="12" t="s">
+      <c r="F161" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G161" s="12"/>
+      <c r="G161" s="13"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="12" t="s">
+      <c r="A162" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="B162" s="12" t="s">
+      <c r="B162" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C162" s="12" t="s">
+      <c r="C162" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D162" s="12" t="s">
+      <c r="D162" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E162" s="12" t="n">
+      <c r="E162" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F162" s="12" t="s">
+      <c r="F162" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G162" s="12"/>
+      <c r="G162" s="13"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
@@ -8386,26 +8406,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="56.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>116</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -9505,22 +9525,22 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>40</v>
       </c>
       <c r="G1" s="3"/>
@@ -9542,7 +9562,7 @@
       <c r="D2" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E2" s="13" t="b">
+      <c r="E2" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9568,7 +9588,7 @@
       <c r="D3" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E3" s="13" t="b">
+      <c r="E3" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9594,7 +9614,7 @@
       <c r="D4" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E4" s="13" t="b">
+      <c r="E4" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9620,7 +9640,7 @@
       <c r="D5" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E5" s="13" t="b">
+      <c r="E5" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9646,7 +9666,7 @@
       <c r="D6" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E6" s="13" t="b">
+      <c r="E6" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9672,7 +9692,7 @@
       <c r="D7" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E7" s="13" t="b">
+      <c r="E7" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9698,7 +9718,7 @@
       <c r="D8" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E8" s="13" t="b">
+      <c r="E8" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9724,7 +9744,7 @@
       <c r="D9" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E9" s="13" t="b">
+      <c r="E9" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9750,7 +9770,7 @@
       <c r="D10" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E10" s="13" t="b">
+      <c r="E10" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9776,7 +9796,7 @@
       <c r="D11" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E11" s="13" t="b">
+      <c r="E11" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9802,7 +9822,7 @@
       <c r="D12" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E12" s="13" t="b">
+      <c r="E12" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9828,7 +9848,7 @@
       <c r="D13" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E13" s="13" t="b">
+      <c r="E13" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9854,7 +9874,7 @@
       <c r="D14" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E14" s="13" t="b">
+      <c r="E14" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9880,7 +9900,7 @@
       <c r="D15" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E15" s="13" t="b">
+      <c r="E15" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9906,7 +9926,7 @@
       <c r="D16" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E16" s="13" t="b">
+      <c r="E16" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -9932,7 +9952,7 @@
       <c r="D17" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E17" s="13" t="b">
+      <c r="E17" s="14" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -10537,19 +10557,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>220</v>
       </c>
       <c r="F1" s="3"/>
@@ -10572,7 +10592,7 @@
       <c r="D2" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="E2" s="14" t="n">
+      <c r="E2" s="15" t="n">
         <f aca="false">D2/SUM($D$2:$D$5)</f>
         <v>0.0422222222222222</v>
       </c>
@@ -10596,7 +10616,7 @@
       <c r="D3" s="3" t="n">
         <v>264</v>
       </c>
-      <c r="E3" s="14" t="n">
+      <c r="E3" s="15" t="n">
         <f aca="false">D3/SUM($D$2:$D$5)</f>
         <v>0.293333333333333</v>
       </c>
@@ -10620,7 +10640,7 @@
       <c r="D4" s="3" t="n">
         <v>502</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <f aca="false">D4/SUM($D$2:$D$5)</f>
         <v>0.557777777777778</v>
       </c>
@@ -10644,7 +10664,7 @@
       <c r="D5" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <f aca="false">D5/SUM($D$2:$D$5)</f>
         <v>0.106666666666667</v>
       </c>
@@ -11397,37 +11417,37 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="9" t="s">
         <v>234</v>
       </c>
     </row>
@@ -11462,7 +11482,7 @@
       <c r="J2" s="3" t="n">
         <v>6542</v>
       </c>
-      <c r="K2" s="14" t="n">
+      <c r="K2" s="15" t="n">
         <v>0.5729</v>
       </c>
     </row>
@@ -11497,7 +11517,7 @@
       <c r="J3" s="3" t="n">
         <v>57714</v>
       </c>
-      <c r="K3" s="14" t="n">
+      <c r="K3" s="15" t="n">
         <v>0.3924</v>
       </c>
     </row>
@@ -11532,7 +11552,7 @@
       <c r="J4" s="3" t="n">
         <v>1660</v>
       </c>
-      <c r="K4" s="14" t="n">
+      <c r="K4" s="15" t="n">
         <v>0.3292</v>
       </c>
     </row>
@@ -11567,7 +11587,7 @@
       <c r="J5" s="3" t="n">
         <v>2293</v>
       </c>
-      <c r="K5" s="14" t="n">
+      <c r="K5" s="15" t="n">
         <v>0.8245</v>
       </c>
     </row>
@@ -11602,7 +11622,7 @@
       <c r="J6" s="3" t="n">
         <v>52882</v>
       </c>
-      <c r="K6" s="14" t="n">
+      <c r="K6" s="15" t="n">
         <v>0.3764</v>
       </c>
     </row>
@@ -11637,7 +11657,7 @@
       <c r="J7" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="K7" s="14" t="n">
+      <c r="K7" s="15" t="n">
         <v>0.9388</v>
       </c>
     </row>
@@ -11672,7 +11692,7 @@
       <c r="J8" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="K8" s="14" t="n">
+      <c r="K8" s="15" t="n">
         <v>0.7363</v>
       </c>
     </row>
@@ -11707,7 +11727,7 @@
       <c r="J9" s="3" t="n">
         <v>956</v>
       </c>
-      <c r="K9" s="14" t="n">
+      <c r="K9" s="15" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -11742,7 +11762,7 @@
       <c r="J10" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="K10" s="14" t="n">
+      <c r="K10" s="15" t="n">
         <v>0.8182</v>
       </c>
     </row>
@@ -11777,7 +11797,7 @@
       <c r="J11" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="K11" s="14" t="n">
+      <c r="K11" s="15" t="n">
         <v>0.7792</v>
       </c>
     </row>
@@ -11812,7 +11832,7 @@
       <c r="J12" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="K12" s="14" t="n">
+      <c r="K12" s="15" t="n">
         <v>0.8469</v>
       </c>
     </row>
@@ -11847,7 +11867,7 @@
       <c r="J13" s="3" t="n">
         <v>3147</v>
       </c>
-      <c r="K13" s="14" t="n">
+      <c r="K13" s="15" t="n">
         <v>0.5076</v>
       </c>
     </row>
@@ -11882,7 +11902,7 @@
       <c r="J14" s="3" t="n">
         <v>7492</v>
       </c>
-      <c r="K14" s="14" t="n">
+      <c r="K14" s="15" t="n">
         <v>0.4824</v>
       </c>
     </row>
@@ -11917,7 +11937,7 @@
       <c r="J15" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="K15" s="14" t="n">
+      <c r="K15" s="15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11952,7 +11972,7 @@
       <c r="J16" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="K16" s="14" t="n">
+      <c r="K16" s="15" t="n">
         <v>0.88</v>
       </c>
     </row>
@@ -11987,7 +12007,7 @@
       <c r="J17" s="3" t="n">
         <v>316</v>
       </c>
-      <c r="K17" s="14" t="n">
+      <c r="K17" s="15" t="n">
         <v>0.9783</v>
       </c>
     </row>
@@ -12007,10 +12027,10 @@
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="0" t="n">
+      <c r="J18" s="8" t="n">
         <v>4917</v>
       </c>
-      <c r="K18" s="14" t="n">
+      <c r="K18" s="15" t="n">
         <f aca="false">ROUND(J18/G18,2)</f>
         <v>0.87</v>
       </c>
@@ -12031,10 +12051,10 @@
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
-      <c r="J19" s="0" t="n">
+      <c r="J19" s="8" t="n">
         <v>2136.8</v>
       </c>
-      <c r="K19" s="14" t="n">
+      <c r="K19" s="15" t="n">
         <f aca="false">ROUND(J19/G19,2)</f>
         <v>0.85</v>
       </c>
@@ -12055,10 +12075,10 @@
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="0" t="n">
+      <c r="J20" s="8" t="n">
         <v>2136.8</v>
       </c>
-      <c r="K20" s="14" t="n">
+      <c r="K20" s="15" t="n">
         <f aca="false">ROUND(J20/G20,2)</f>
         <v>0.85</v>
       </c>
@@ -12079,10 +12099,10 @@
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
-      <c r="J21" s="0" t="n">
+      <c r="J21" s="8" t="n">
         <v>2136.8</v>
       </c>
-      <c r="K21" s="14" t="n">
+      <c r="K21" s="15" t="n">
         <f aca="false">ROUND(J21/G21,2)</f>
         <v>0.85</v>
       </c>
@@ -12103,10 +12123,10 @@
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-      <c r="J22" s="0" t="n">
+      <c r="J22" s="8" t="n">
         <v>2136.8</v>
       </c>
-      <c r="K22" s="14" t="n">
+      <c r="K22" s="15" t="n">
         <f aca="false">ROUND(J22/G22,2)</f>
         <v>0.85</v>
       </c>
@@ -12127,10 +12147,10 @@
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="J23" s="0" t="n">
+      <c r="J23" s="8" t="n">
         <v>4917</v>
       </c>
-      <c r="K23" s="14" t="n">
+      <c r="K23" s="15" t="n">
         <f aca="false">ROUND(J23/G23,2)</f>
         <v>0.87</v>
       </c>
@@ -12151,10 +12171,10 @@
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-      <c r="J24" s="0" t="n">
+      <c r="J24" s="8" t="n">
         <v>2136.8</v>
       </c>
-      <c r="K24" s="14" t="n">
+      <c r="K24" s="15" t="n">
         <f aca="false">ROUND(J24/G24,2)</f>
         <v>0.85</v>
       </c>
@@ -12199,7 +12219,7 @@
         <f aca="false">SUM(J2:J24)</f>
         <v>154036</v>
       </c>
-      <c r="K25" s="14" t="n">
+      <c r="K25" s="15" t="n">
         <f aca="false">ROUND(J25/G25,2)</f>
         <v>0.43</v>
       </c>
@@ -12775,2251 +12795,2251 @@
   <dimension ref="A1:F121"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="16" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="16"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="17" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="16"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="16"/>
+      <c r="F5" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="17" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="17" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="16"/>
+      <c r="F8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="17" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="17" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="16"/>
+      <c r="F11" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="17" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="16"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="17" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="16"/>
+      <c r="F15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="17" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="16"/>
+      <c r="F17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="17" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="16"/>
+      <c r="F19" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="16"/>
+      <c r="F20" s="17"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="16"/>
+      <c r="F21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F22" s="16"/>
+      <c r="F22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="17" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="16"/>
+      <c r="F24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="F25" s="17" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F26" s="16"/>
+      <c r="F26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F27" s="16"/>
+      <c r="F27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="16"/>
+      <c r="F28" s="17"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="16"/>
+      <c r="F29" s="17"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="16" t="s">
+      <c r="F30" s="17" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F31" s="16"/>
+      <c r="F31" s="17"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="17" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F33" s="16"/>
+      <c r="F33" s="17"/>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E34" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F34" s="16"/>
+      <c r="E34" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F34" s="17"/>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E35" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F35" s="16"/>
+      <c r="E35" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F35" s="17"/>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E36" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F36" s="16"/>
+      <c r="E36" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F36" s="17"/>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D37" s="17" t="n">
+      <c r="D37" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E37" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F37" s="16"/>
+      <c r="E37" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" s="17"/>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F38" s="16"/>
+      <c r="E38" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38" s="17"/>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D39" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E39" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F39" s="16"/>
+      <c r="E39" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F39" s="17"/>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D40" s="17" t="n">
+      <c r="D40" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E40" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F40" s="16"/>
+      <c r="E40" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F40" s="17"/>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D41" s="17" t="n">
+      <c r="D41" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F41" s="16"/>
+      <c r="E41" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F41" s="17"/>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D42" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="E42" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F42" s="16"/>
+      <c r="E42" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F42" s="17"/>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D43" s="17" t="n">
+      <c r="D43" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="E43" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F43" s="16"/>
+      <c r="E43" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F43" s="17"/>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D44" s="17" t="n">
+      <c r="D44" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E44" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F44" s="16"/>
+      <c r="E44" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" s="17"/>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D45" s="17" t="n">
+      <c r="D45" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E45" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F45" s="16"/>
+      <c r="E45" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F45" s="17"/>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D46" s="17" t="n">
+      <c r="D46" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E46" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F46" s="16"/>
+      <c r="E46" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F46" s="17"/>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="17" t="n">
+      <c r="D47" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E47" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F47" s="16"/>
+      <c r="E47" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F47" s="17"/>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D48" s="17" t="n">
+      <c r="D48" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E48" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F48" s="16"/>
+      <c r="E48" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F48" s="17"/>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D49" s="17" t="n">
+      <c r="D49" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E49" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F49" s="16"/>
+      <c r="E49" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F49" s="17"/>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D50" s="17" t="n">
+      <c r="D50" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E50" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F50" s="16"/>
+      <c r="E50" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F50" s="17"/>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D51" s="17" t="n">
+      <c r="D51" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="E51" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F51" s="16"/>
+      <c r="E51" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F51" s="17"/>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D52" s="17" t="n">
+      <c r="D52" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="E52" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F52" s="16"/>
+      <c r="E52" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F52" s="17"/>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D53" s="17" t="n">
+      <c r="D53" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="E53" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F53" s="16"/>
+      <c r="E53" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F53" s="17"/>
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C54" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D54" s="17" t="n">
+      <c r="D54" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E54" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F54" s="16"/>
+      <c r="E54" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F54" s="17"/>
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C55" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D55" s="17" t="n">
+      <c r="D55" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E55" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F55" s="16"/>
+      <c r="E55" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F55" s="17"/>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B56" s="16" t="s">
+      <c r="B56" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C56" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D56" s="17" t="n">
+      <c r="D56" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E56" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F56" s="16"/>
+      <c r="E56" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F56" s="17"/>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="B57" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D57" s="17" t="n">
+      <c r="D57" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F57" s="16"/>
+      <c r="E57" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F57" s="17"/>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="16" t="s">
+      <c r="A58" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C58" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D58" s="17" t="n">
+      <c r="D58" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E58" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F58" s="16"/>
+      <c r="E58" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F58" s="17"/>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="C59" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D59" s="17" t="n">
+      <c r="D59" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E59" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F59" s="16"/>
+      <c r="E59" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F59" s="17"/>
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="16" t="s">
+      <c r="A60" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B60" s="16" t="s">
+      <c r="B60" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C60" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D60" s="17" t="n">
+      <c r="D60" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="E60" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F60" s="16"/>
+      <c r="E60" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F60" s="17"/>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="16" t="s">
+      <c r="A61" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C61" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D61" s="17" t="n">
+      <c r="D61" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="E61" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F61" s="16"/>
+      <c r="E61" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F61" s="17"/>
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B62" s="16" t="s">
+      <c r="B62" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C62" s="16" t="s">
+      <c r="C62" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D62" s="17" t="n">
+      <c r="D62" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="E62" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F62" s="16"/>
+      <c r="E62" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F62" s="17"/>
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="16" t="s">
+      <c r="A63" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B63" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C63" s="16" t="s">
+      <c r="C63" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D63" s="17" t="n">
+      <c r="D63" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E63" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F63" s="16"/>
+      <c r="E63" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F63" s="17"/>
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="16" t="s">
+      <c r="A64" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="C64" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D64" s="17" t="n">
+      <c r="D64" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E64" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F64" s="16"/>
+      <c r="E64" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F64" s="17"/>
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="16" t="s">
+      <c r="A65" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C65" s="16" t="s">
+      <c r="C65" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D65" s="17" t="n">
+      <c r="D65" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E65" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F65" s="16"/>
+      <c r="E65" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F65" s="17"/>
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="16" t="s">
+      <c r="A66" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="B66" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D66" s="17" t="n">
+      <c r="D66" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E66" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F66" s="16"/>
+      <c r="E66" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F66" s="17"/>
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="B67" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C67" s="16" t="s">
+      <c r="C67" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D67" s="17" t="n">
+      <c r="D67" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E67" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F67" s="16"/>
+      <c r="E67" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F67" s="17"/>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C68" s="16" t="s">
+      <c r="C68" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D68" s="17" t="n">
+      <c r="D68" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E68" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F68" s="16"/>
+      <c r="E68" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F68" s="17"/>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="B69" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="C69" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D69" s="17" t="n">
+      <c r="D69" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="E69" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F69" s="16"/>
+      <c r="E69" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F69" s="17"/>
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="16" t="s">
+      <c r="B70" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="16" t="s">
+      <c r="C70" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D70" s="17" t="n">
+      <c r="D70" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="E70" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F70" s="16"/>
+      <c r="E70" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F70" s="17"/>
     </row>
     <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="16" t="s">
+      <c r="A71" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B71" s="16" t="s">
+      <c r="B71" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C71" s="16" t="s">
+      <c r="C71" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D71" s="17" t="n">
+      <c r="D71" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E71" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F71" s="16"/>
+      <c r="E71" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F71" s="17"/>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="16" t="s">
+      <c r="A72" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="16" t="s">
+      <c r="B72" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C72" s="16" t="s">
+      <c r="C72" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D72" s="17" t="n">
+      <c r="D72" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E72" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F72" s="16"/>
+      <c r="E72" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F72" s="17"/>
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B73" s="16" t="s">
+      <c r="B73" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C73" s="16" t="s">
+      <c r="C73" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D73" s="17" t="n">
+      <c r="D73" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E73" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F73" s="16"/>
+      <c r="E73" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F73" s="17"/>
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="16" t="s">
+      <c r="A74" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B74" s="16" t="s">
+      <c r="B74" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C74" s="16" t="s">
+      <c r="C74" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D74" s="17" t="n">
+      <c r="D74" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E74" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F74" s="16"/>
+      <c r="E74" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F74" s="17"/>
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B75" s="16" t="s">
+      <c r="B75" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C75" s="16" t="s">
+      <c r="C75" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D75" s="17" t="n">
+      <c r="D75" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E75" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F75" s="16"/>
+      <c r="E75" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F75" s="17"/>
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="16" t="s">
+      <c r="B76" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C76" s="16" t="s">
+      <c r="C76" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D76" s="17" t="n">
+      <c r="D76" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E76" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F76" s="16"/>
+      <c r="E76" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F76" s="17"/>
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B77" s="16" t="s">
+      <c r="B77" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C77" s="16" t="s">
+      <c r="C77" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D77" s="17" t="n">
+      <c r="D77" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E77" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F77" s="16"/>
+      <c r="E77" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F77" s="17"/>
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="16" t="s">
+      <c r="A78" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B78" s="16" t="s">
+      <c r="B78" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C78" s="16" t="s">
+      <c r="C78" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D78" s="17" t="n">
+      <c r="D78" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="E78" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F78" s="16"/>
+      <c r="E78" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F78" s="17"/>
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B79" s="16" t="s">
+      <c r="B79" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="C79" s="16" t="s">
+      <c r="C79" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D79" s="17" t="n">
+      <c r="D79" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E79" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F79" s="16"/>
+      <c r="E79" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F79" s="17"/>
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="16" t="s">
+      <c r="A80" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B80" s="16" t="s">
+      <c r="B80" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C80" s="16" t="s">
+      <c r="C80" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D80" s="17" t="n">
+      <c r="D80" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E80" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F80" s="16"/>
+      <c r="E80" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F80" s="17"/>
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="16" t="s">
+      <c r="A81" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B81" s="16" t="s">
+      <c r="B81" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C81" s="16" t="s">
+      <c r="C81" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D81" s="17" t="n">
+      <c r="D81" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E81" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F81" s="16"/>
+      <c r="E81" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F81" s="17"/>
     </row>
     <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="16" t="s">
+      <c r="A82" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B82" s="16" t="s">
+      <c r="B82" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C82" s="16" t="s">
+      <c r="C82" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D82" s="17" t="n">
+      <c r="D82" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E82" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F82" s="16"/>
+      <c r="E82" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F82" s="17"/>
     </row>
     <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="16" t="s">
+      <c r="A83" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B83" s="16" t="s">
+      <c r="B83" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C83" s="16" t="s">
+      <c r="C83" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D83" s="17" t="n">
+      <c r="D83" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E83" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F83" s="16"/>
+      <c r="E83" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F83" s="17"/>
     </row>
     <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="16" t="s">
+      <c r="A84" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B84" s="16" t="s">
+      <c r="B84" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C84" s="16" t="s">
+      <c r="C84" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D84" s="17" t="n">
+      <c r="D84" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E84" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F84" s="16"/>
+      <c r="E84" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F84" s="17"/>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="16" t="s">
+      <c r="A85" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B85" s="16" t="s">
+      <c r="B85" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C85" s="16" t="s">
+      <c r="C85" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D85" s="17" t="n">
+      <c r="D85" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E85" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F85" s="16"/>
+      <c r="E85" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F85" s="17"/>
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="16" t="s">
+      <c r="A86" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B86" s="16" t="s">
+      <c r="B86" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C86" s="16" t="s">
+      <c r="C86" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D86" s="17" t="n">
+      <c r="D86" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E86" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F86" s="16"/>
+      <c r="E86" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F86" s="17"/>
     </row>
     <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="16" t="s">
+      <c r="A87" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B87" s="16" t="s">
+      <c r="B87" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C87" s="16" t="s">
+      <c r="C87" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D87" s="17" t="n">
+      <c r="D87" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="E87" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F87" s="16"/>
+      <c r="E87" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F87" s="17"/>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="16" t="s">
+      <c r="A88" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B88" s="16" t="s">
+      <c r="B88" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C88" s="16" t="s">
+      <c r="C88" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D88" s="17" t="n">
+      <c r="D88" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E88" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F88" s="16"/>
+      <c r="E88" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F88" s="17"/>
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="16" t="s">
+      <c r="A89" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B89" s="16" t="s">
+      <c r="B89" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C89" s="16" t="s">
+      <c r="C89" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D89" s="17" t="n">
+      <c r="D89" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E89" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F89" s="16"/>
+      <c r="E89" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F89" s="17"/>
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="16" t="s">
+      <c r="A90" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B90" s="16" t="s">
+      <c r="B90" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C90" s="16" t="s">
+      <c r="C90" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D90" s="17" t="n">
+      <c r="D90" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E90" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F90" s="16"/>
+      <c r="E90" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F90" s="17"/>
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="16" t="s">
+      <c r="A91" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B91" s="16" t="s">
+      <c r="B91" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C91" s="16" t="s">
+      <c r="C91" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D91" s="17" t="n">
+      <c r="D91" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E91" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F91" s="16"/>
+      <c r="E91" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F91" s="17"/>
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="16" t="s">
+      <c r="A92" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B92" s="16" t="s">
+      <c r="B92" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C92" s="16" t="s">
+      <c r="C92" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D92" s="17" t="n">
+      <c r="D92" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E92" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F92" s="16"/>
+      <c r="E92" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F92" s="17"/>
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="16" t="s">
+      <c r="A93" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B93" s="16" t="s">
+      <c r="B93" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C93" s="16" t="s">
+      <c r="C93" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D93" s="17" t="n">
+      <c r="D93" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E93" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F93" s="16"/>
+      <c r="E93" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F93" s="17"/>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="16" t="s">
+      <c r="A94" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B94" s="16" t="s">
+      <c r="B94" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C94" s="16" t="s">
+      <c r="C94" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D94" s="17" t="n">
+      <c r="D94" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E94" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F94" s="16"/>
+      <c r="E94" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F94" s="17"/>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="16" t="s">
+      <c r="A95" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B95" s="16" t="s">
+      <c r="B95" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C95" s="16" t="s">
+      <c r="C95" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D95" s="17" t="n">
+      <c r="D95" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E95" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F95" s="16"/>
+      <c r="E95" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F95" s="17"/>
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="16" t="s">
+      <c r="A96" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B96" s="16" t="s">
+      <c r="B96" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C96" s="16" t="s">
+      <c r="C96" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D96" s="17" t="n">
+      <c r="D96" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="E96" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F96" s="16"/>
+      <c r="E96" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F96" s="17"/>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="16" t="s">
+      <c r="A97" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B97" s="16" t="s">
+      <c r="B97" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C97" s="16" t="s">
+      <c r="C97" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D97" s="17" t="n">
+      <c r="D97" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E97" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F97" s="16"/>
+      <c r="E97" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F97" s="17"/>
     </row>
     <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="16" t="s">
+      <c r="A98" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B98" s="16" t="s">
+      <c r="B98" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C98" s="16" t="s">
+      <c r="C98" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D98" s="17" t="n">
+      <c r="D98" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E98" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F98" s="16"/>
+      <c r="E98" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F98" s="17"/>
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="16" t="s">
+      <c r="A99" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B99" s="16" t="s">
+      <c r="B99" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C99" s="16" t="s">
+      <c r="C99" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D99" s="17" t="n">
+      <c r="D99" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E99" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F99" s="16"/>
+      <c r="E99" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F99" s="17"/>
     </row>
     <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="16" t="s">
+      <c r="A100" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B100" s="16" t="s">
+      <c r="B100" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C100" s="16" t="s">
+      <c r="C100" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D100" s="17" t="n">
+      <c r="D100" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E100" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F100" s="16"/>
+      <c r="E100" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F100" s="17"/>
     </row>
     <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="16" t="s">
+      <c r="A101" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B101" s="16" t="s">
+      <c r="B101" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C101" s="16" t="s">
+      <c r="C101" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D101" s="17" t="n">
+      <c r="D101" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E101" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F101" s="16"/>
+      <c r="E101" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F101" s="17"/>
     </row>
     <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="16" t="s">
+      <c r="A102" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B102" s="16" t="s">
+      <c r="B102" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C102" s="16" t="s">
+      <c r="C102" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D102" s="17" t="n">
+      <c r="D102" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E102" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F102" s="16"/>
+      <c r="E102" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F102" s="17"/>
     </row>
     <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="16" t="s">
+      <c r="A103" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B103" s="16" t="s">
+      <c r="B103" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C103" s="16" t="s">
+      <c r="C103" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D103" s="17" t="n">
+      <c r="D103" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E103" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F103" s="16"/>
+      <c r="E103" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F103" s="17"/>
     </row>
     <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="16" t="s">
+      <c r="A104" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B104" s="16" t="s">
+      <c r="B104" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C104" s="16" t="s">
+      <c r="C104" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D104" s="17" t="n">
+      <c r="D104" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E104" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F104" s="16"/>
+      <c r="E104" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F104" s="17"/>
     </row>
     <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="16" t="s">
+      <c r="A105" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B105" s="16" t="s">
+      <c r="B105" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C105" s="16" t="s">
+      <c r="C105" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D105" s="17" t="n">
+      <c r="D105" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E105" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F105" s="16" t="s">
+      <c r="E105" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F105" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="16" t="s">
+      <c r="A106" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B106" s="16" t="s">
+      <c r="B106" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C106" s="16" t="s">
+      <c r="C106" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D106" s="17" t="n">
+      <c r="D106" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E106" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F106" s="16" t="s">
+      <c r="E106" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F106" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="16" t="s">
+      <c r="A107" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B107" s="16" t="s">
+      <c r="B107" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C107" s="16" t="s">
+      <c r="C107" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D107" s="17" t="n">
+      <c r="D107" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E107" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F107" s="16" t="s">
+      <c r="E107" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F107" s="17" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="16" t="s">
+      <c r="A108" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B108" s="16" t="s">
+      <c r="B108" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C108" s="16" t="s">
+      <c r="C108" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D108" s="17" t="n">
+      <c r="D108" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E108" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F108" s="16" t="s">
+      <c r="E108" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F108" s="17" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="16" t="s">
+      <c r="A109" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="B109" s="16" t="s">
+      <c r="B109" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C109" s="16" t="s">
+      <c r="C109" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D109" s="17" t="n">
+      <c r="D109" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="E109" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F109" s="16" t="s">
+      <c r="E109" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F109" s="17" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="16" t="s">
+      <c r="A110" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="B110" s="16" t="s">
+      <c r="B110" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C110" s="16" t="s">
+      <c r="C110" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D110" s="17" t="n">
+      <c r="D110" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E110" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F110" s="16" t="s">
+      <c r="E110" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F110" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="16" t="s">
+      <c r="A111" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="B111" s="16" t="s">
+      <c r="B111" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C111" s="16" t="s">
+      <c r="C111" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D111" s="17" t="n">
+      <c r="D111" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E111" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F111" s="16" t="s">
+      <c r="E111" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F111" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="16" t="s">
+      <c r="A112" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B112" s="16" t="s">
+      <c r="B112" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C112" s="16" t="s">
+      <c r="C112" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D112" s="17" t="n">
+      <c r="D112" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="E112" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F112" s="16" t="s">
+      <c r="E112" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F112" s="17" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="16" t="s">
+      <c r="A113" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B113" s="16" t="s">
+      <c r="B113" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C113" s="16" t="s">
+      <c r="C113" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D113" s="17" t="n">
+      <c r="D113" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E113" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F113" s="16" t="s">
+      <c r="E113" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F113" s="17" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="16" t="s">
+      <c r="A114" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B114" s="16" t="s">
+      <c r="B114" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C114" s="16" t="s">
+      <c r="C114" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D114" s="17" t="n">
+      <c r="D114" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E114" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F114" s="16" t="s">
+      <c r="E114" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F114" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="16" t="s">
+      <c r="A115" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B115" s="16" t="s">
+      <c r="B115" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C115" s="16" t="s">
+      <c r="C115" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D115" s="17" t="n">
+      <c r="D115" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E115" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F115" s="16" t="s">
+      <c r="E115" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F115" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="16" t="s">
+      <c r="A116" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B116" s="16" t="s">
+      <c r="B116" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C116" s="16" t="s">
+      <c r="C116" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D116" s="17" t="n">
+      <c r="D116" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="E116" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F116" s="16" t="s">
+      <c r="E116" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F116" s="17" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="16" t="s">
+      <c r="A117" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B117" s="16" t="s">
+      <c r="B117" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C117" s="16" t="s">
+      <c r="C117" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D117" s="17" t="n">
+      <c r="D117" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E117" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F117" s="16" t="s">
+      <c r="E117" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F117" s="17" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="16" t="s">
+      <c r="A118" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B118" s="16" t="s">
+      <c r="B118" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C118" s="16" t="s">
+      <c r="C118" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D118" s="17" t="n">
+      <c r="D118" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E118" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F118" s="16" t="s">
+      <c r="E118" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F118" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="16" t="s">
+      <c r="A119" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B119" s="16" t="s">
+      <c r="B119" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C119" s="16" t="s">
+      <c r="C119" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D119" s="17" t="n">
+      <c r="D119" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E119" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F119" s="16" t="s">
+      <c r="E119" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F119" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="16" t="s">
+      <c r="A120" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="B120" s="16" t="s">
+      <c r="B120" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C120" s="16" t="s">
+      <c r="C120" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D120" s="17" t="n">
+      <c r="D120" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="E120" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F120" s="16" t="s">
+      <c r="E120" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F120" s="17" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="16" t="s">
+      <c r="A121" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="B121" s="16" t="s">
+      <c r="B121" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C121" s="16" t="s">
+      <c r="C121" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D121" s="17" t="n">
+      <c r="D121" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E121" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F121" s="16" t="s">
+      <c r="E121" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F121" s="17" t="s">
         <v>104</v>
       </c>
     </row>
@@ -15042,380 +15062,380 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="55"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>250</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="17" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>250</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="17" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="17" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="17" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="17" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="17" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="17" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="17" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="17" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="17" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="21" t="s">
         <v>271</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="17" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="17" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="17" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="17" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="17" t="s">
         <v>282</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="17" t="s">
         <v>280</v>
       </c>
     </row>

--- a/parametres_simulateur_inphb.xlsx
+++ b/parametres_simulateur_inphb.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2217" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="273">
   <si>
     <t xml:space="preserve">Simulateur INP-HB, fichiers de paramétrage</t>
   </si>
@@ -549,40 +549,10 @@
     <t xml:space="preserve">Brochure p.3</t>
   </si>
   <si>
-    <t xml:space="preserve">GMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestion commerciale, Marketing et Communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestion des Ressources Humaines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestion de la Supply Chain</t>
-  </si>
-  <si>
     <t xml:space="preserve">Finance, Comptabilité et Assurance</t>
   </si>
   <si>
     <t xml:space="preserve">B,C,D,G2,BTCOMPTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comptabilité et Contrôle, Audit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banque, Finance et Assurance</t>
   </si>
   <si>
     <t xml:space="preserve">EIT, INFO</t>
@@ -1335,7 +1305,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TblEligibilite" displayName="TblEligibilite" ref="A1:F22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TblEligibilite" displayName="TblEligibilite" ref="A1:F17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" name="cycle"/>
     <tableColumn id="2" name="ecole"/>
@@ -8397,7 +8367,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K1048576"/>
   <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.89"/>
@@ -8471,19 +8441,19 @@
         <v>122</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>172</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -8495,22 +8465,22 @@
         <v>118</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>172</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -8522,22 +8492,22 @@
         <v>118</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>172</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -8549,10 +8519,10 @@
         <v>118</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>179</v>
@@ -8564,7 +8534,7 @@
         <v>172</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -8576,22 +8546,22 @@
         <v>118</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>172</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -8603,22 +8573,22 @@
         <v>118</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>172</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -8630,22 +8600,22 @@
         <v>118</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>172</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -8657,22 +8627,22 @@
         <v>118</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>172</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -8684,22 +8654,22 @@
         <v>118</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>172</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -8708,25 +8678,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>191</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -8735,25 +8705,25 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>193</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="G13" s="3" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -8762,13 +8732,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>194</v>
@@ -8777,10 +8747,10 @@
         <v>195</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -8789,25 +8759,25 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>196</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>197</v>
+        <v>149</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -8816,25 +8786,25 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>129</v>
+        <v>190</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -8846,155 +8816,85 @@
         <v>123</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>133</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>124</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>140</v>
-      </c>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>134</v>
-      </c>
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>138</v>
-      </c>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>202</v>
-      </c>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -9430,71 +9330,11 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-    </row>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9535,10 +9375,10 @@
         <v>16</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>40</v>
@@ -9567,7 +9407,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -9593,7 +9433,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -9619,7 +9459,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -9645,7 +9485,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -9671,7 +9511,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -9684,7 +9524,7 @@
         <v>123</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
@@ -9697,7 +9537,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -9710,7 +9550,7 @@
         <v>118</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -9723,7 +9563,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -9736,7 +9576,7 @@
         <v>118</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
@@ -9749,7 +9589,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -9775,7 +9615,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -9801,7 +9641,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -9827,7 +9667,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -9853,7 +9693,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
@@ -9879,7 +9719,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
@@ -9905,7 +9745,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
@@ -9931,7 +9771,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
@@ -9957,7 +9797,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
@@ -10558,19 +10398,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -10581,7 +10421,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>10</v>
@@ -10605,7 +10445,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>12</v>
@@ -10629,7 +10469,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>14</v>
@@ -10653,7 +10493,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>16</v>
@@ -11421,34 +11261,34 @@
         <v>36</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11838,7 +11678,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>5662</v>
@@ -11908,7 +11748,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>31</v>
@@ -11943,7 +11783,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>21</v>
@@ -11978,7 +11818,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>206</v>
@@ -12181,7 +12021,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B25" s="3" t="n">
         <f aca="false">SUM(B2:B24)</f>
@@ -12808,13 +12648,13 @@
         <v>36</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E1" s="16" t="s">
         <v>39</v>
@@ -15073,7 +14913,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="B1" s="20" t="s">
         <v>117</v>
@@ -15082,13 +14922,13 @@
         <v>112</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>40</v>
@@ -15102,19 +14942,19 @@
         <v>122</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15125,19 +14965,19 @@
         <v>122</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15145,22 +14985,22 @@
         <v>124</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15168,22 +15008,22 @@
         <v>133</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15191,22 +15031,22 @@
         <v>134</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15214,22 +15054,22 @@
         <v>138</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15237,22 +15077,22 @@
         <v>140</v>
       </c>
       <c r="B8" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>263</v>
-      </c>
       <c r="E8" s="21" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15263,19 +15103,19 @@
         <v>129</v>
       </c>
       <c r="C9" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="F9" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>257</v>
-      </c>
       <c r="G9" s="17" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15286,19 +15126,19 @@
         <v>153</v>
       </c>
       <c r="C10" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="F10" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>257</v>
-      </c>
       <c r="G10" s="17" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15309,19 +15149,19 @@
         <v>153</v>
       </c>
       <c r="C11" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="F11" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>257</v>
-      </c>
       <c r="G11" s="17" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15332,19 +15172,19 @@
         <v>157</v>
       </c>
       <c r="C12" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="F12" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D12" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>257</v>
-      </c>
       <c r="G12" s="17" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15355,19 +15195,19 @@
         <v>159</v>
       </c>
       <c r="C13" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="F13" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>274</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>257</v>
-      </c>
       <c r="G13" s="17" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15378,19 +15218,19 @@
         <v>161</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15401,19 +15241,19 @@
         <v>161</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15424,19 +15264,19 @@
         <v>164</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/parametres_simulateur_inphb.xlsx
+++ b/parametres_simulateur_inphb.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2273" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2280" uniqueCount="278">
   <si>
     <t xml:space="preserve">Simulateur INP-HB, fichiers de paramétrage</t>
   </si>
@@ -2431,7 +2431,7 @@
   <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="39.73"/>
@@ -12109,130 +12109,217 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>171972</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>171820</v>
-      </c>
+      <c r="A18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
       <c r="D18" s="3" t="n">
-        <v>343792</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>167028</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>165487</v>
-      </c>
+        <v>5666</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
       <c r="G18" s="3" t="n">
-        <v>332515</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>68883</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>64635</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>133518</v>
+        <v>5666</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="8" t="n">
+        <v>4917</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0.4015</v>
+        <f aca="false">ROUND(J18/G18,2)</f>
+        <v>0.87</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3"/>
+      <c r="A19" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="D19" s="3" t="n">
+        <v>2499.6</v>
+      </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="G19" s="3" t="n">
+        <v>2499.6</v>
+      </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
+      <c r="J19" s="8" t="n">
+        <v>2136.8</v>
+      </c>
+      <c r="K19" s="15" t="n">
+        <f aca="false">ROUND(J19/G19,2)</f>
+        <v>0.85</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3"/>
+      <c r="A20" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3" t="n">
+        <v>2499.6</v>
+      </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="G20" s="3" t="n">
+        <v>2499.6</v>
+      </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
+      <c r="J20" s="8" t="n">
+        <v>2136.8</v>
+      </c>
+      <c r="K20" s="15" t="n">
+        <f aca="false">ROUND(J20/G20,2)</f>
+        <v>0.85</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
+      <c r="A21" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3" t="n">
+        <v>2499.6</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+      <c r="G21" s="3" t="n">
+        <v>2499.6</v>
+      </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="J21" s="8" t="n">
+        <v>2136.8</v>
+      </c>
+      <c r="K21" s="15" t="n">
+        <f aca="false">ROUND(J21/G21,2)</f>
+        <v>0.85</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
+      <c r="A22" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="D22" s="3" t="n">
+        <v>2499.6</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
+      <c r="G22" s="3" t="n">
+        <v>2499.6</v>
+      </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
+      <c r="J22" s="8" t="n">
+        <v>2136.8</v>
+      </c>
+      <c r="K22" s="15" t="n">
+        <f aca="false">ROUND(J22/G22,2)</f>
+        <v>0.85</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3"/>
+      <c r="A23" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="D23" s="3" t="n">
+        <v>5666</v>
+      </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="G23" s="3" t="n">
+        <v>5666</v>
+      </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
+      <c r="J23" s="8" t="n">
+        <v>4917</v>
+      </c>
+      <c r="K23" s="15" t="n">
+        <f aca="false">ROUND(J23/G23,2)</f>
+        <v>0.87</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3"/>
+      <c r="A24" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="D24" s="3" t="n">
+        <v>2499.6</v>
+      </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
+      <c r="G24" s="3" t="n">
+        <v>2499.6</v>
+      </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
+      <c r="J24" s="8" t="n">
+        <v>2136.8</v>
+      </c>
+      <c r="K24" s="15" t="n">
+        <f aca="false">ROUND(J24/G24,2)</f>
+        <v>0.85</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <f aca="false">SUM(B2:B24)</f>
+        <v>171972</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <f aca="false">SUM(C2:C24)</f>
+        <v>171820</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <f aca="false">SUM(D2:D24)</f>
+        <v>367622</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <f aca="false">SUM(E2:E24)</f>
+        <v>167028</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <f aca="false">SUM(F2:F24)</f>
+        <v>165487</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <f aca="false">SUM(G2:G24)</f>
+        <v>356345</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <f aca="false">SUM(H2:H24)</f>
+        <v>68883</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <f aca="false">SUM(I2:I24)</f>
+        <v>64635</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <f aca="false">SUM(J2:J24)</f>
+        <v>154036</v>
+      </c>
+      <c r="K25" s="15" t="n">
+        <f aca="false">ROUND(J25/G25,2)</f>
+        <v>0.43</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
@@ -14702,7 +14789,7 @@
       <c r="B109" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C109" s="0" t="s">
+      <c r="C109" s="8" t="s">
         <v>132</v>
       </c>
       <c r="D109" s="1" t="n">

--- a/parametres_simulateur_inphb.xlsx
+++ b/parametres_simulateur_inphb.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
@@ -813,7 +813,7 @@
     <t xml:space="preserve">Gestion appliquée aux entreprises</t>
   </si>
   <si>
-    <t xml:space="preserve">https://escae.inphb.ci/public/formations</t>
+    <t xml:space="preserve">https://escae.inphb.ci/public/formations/cycle-technicien-superieur</t>
   </si>
   <si>
     <t xml:space="preserve">Page de l'école</t>
@@ -834,7 +834,7 @@
     <t xml:space="preserve">Économique et commerciale générale</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.inphb.ci/static/media/CPGE.9b4d786a11dd59ac7ac1.pdf</t>
+    <t xml:space="preserve">https://inphb.edu.ci/nos-ecoles/cpge/filieres/</t>
   </si>
   <si>
     <t xml:space="preserve">Plaquette officielle</t>
@@ -900,7 +900,7 @@
     <t xml:space="preserve">Procédés et maîtrise de l'énergie</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.inphb.ci/</t>
+    <t xml:space="preserve">https://inphb.edu.ci/nos-ecoles/</t>
   </si>
   <si>
     <t xml:space="preserve">Site officiel INP-HB</t>
